--- a/config/Excel/NPC.xlsx
+++ b/config/Excel/NPC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DD928C-7DAC-4007-B698-E7E9F2823854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880CFE41-DE21-4658-957B-59AC0224A766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="290">
   <si>
     <t>NPC識別碼</t>
   </si>
@@ -918,6 +918,80 @@
   </si>
   <si>
     <t>god_chaos</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>移動速度</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>米</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>秒</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻擊距離(米)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻擊速度(次/秒)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -925,7 +999,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -955,6 +1029,29 @@
     <font>
       <sz val="11"/>
       <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
       <family val="2"/>
       <charset val="136"/>
     </font>
@@ -1015,7 +1112,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1040,12 +1137,121 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9E2F3"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9E2F3"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9E2F3"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1059,13 +1265,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NPCTable" displayName="NPCTable" ref="A1:G85" totalsRowShown="0">
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NPCTable" displayName="NPCTable" ref="A1:J85" totalsRowShown="0">
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="NPC識別碼"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="NPC名稱"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="所屬地圖識別碼"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="屬性"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="外觀"/>
+    <tableColumn id="10" xr3:uid="{6F874BA1-FF6B-4646-B1EE-72FFC55222C6}" name="移動速度(米/秒)" dataDxfId="2" dataCellStyle="Normal"/>
+    <tableColumn id="9" xr3:uid="{E04420AF-891B-480A-9ED8-4D87846DE54E}" name="攻擊速度(次/秒)" dataDxfId="0" dataCellStyle="Normal"/>
+    <tableColumn id="8" xr3:uid="{4BEE5E3D-977E-470C-BC00-4A996DB00A9E}" name="攻擊距離(米)" dataDxfId="1" dataCellStyle="Normal"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="魔法型（1是／0否）"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="出現權重"/>
   </tableColumns>
@@ -1268,20 +1477,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="13" max="13" width="12.25" customWidth="1"/>
+    <col min="5" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="15" max="15" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="39.6" customHeight="1">
+    <row r="1" spans="1:10" ht="39.6" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1297,14 +1506,23 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1">
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>38</v>
       </c>
@@ -1320,14 +1538,23 @@
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="4">
-        <v>1</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="F2" s="3">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H2" s="3">
+        <v>24</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1</v>
+      </c>
+      <c r="J2" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" customHeight="1">
+    <row r="3" spans="1:10" ht="15" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
@@ -1343,14 +1570,23 @@
       <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" customHeight="1">
+      <c r="F3" s="3">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>6</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>42</v>
       </c>
@@ -1366,14 +1602,23 @@
       <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="4">
-        <v>1</v>
-      </c>
-      <c r="G4" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1">
+      <c r="F4" s="3">
+        <v>24</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H4" s="3">
+        <v>6</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>43</v>
       </c>
@@ -1389,14 +1634,23 @@
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" customHeight="1">
+      <c r="F5" s="3">
+        <v>6</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3">
+        <v>6</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>44</v>
       </c>
@@ -1412,14 +1666,23 @@
       <c r="E6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="4">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" customHeight="1">
+      <c r="F6" s="3">
+        <v>18</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>24</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1</v>
+      </c>
+      <c r="J6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>46</v>
       </c>
@@ -1435,14 +1698,23 @@
       <c r="E7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="4">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" customHeight="1">
+      <c r="F7" s="3">
+        <v>12</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H7" s="3">
+        <v>6</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>48</v>
       </c>
@@ -1458,14 +1730,23 @@
       <c r="E8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="4">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4">
+      <c r="F8" s="3">
+        <v>12</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>6</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" customHeight="1">
+    <row r="9" spans="1:10" ht="15" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
@@ -1481,14 +1762,23 @@
       <c r="E9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="4">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" customHeight="1">
+      <c r="F9" s="3">
+        <v>24</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H9" s="3">
+        <v>6</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>50</v>
       </c>
@@ -1504,14 +1794,23 @@
       <c r="E10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="4">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1">
+      <c r="F10" s="3">
+        <v>6</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H10" s="3">
+        <v>24</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
+      <c r="J10" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>52</v>
       </c>
@@ -1527,14 +1826,23 @@
       <c r="E11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="4">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" customHeight="1">
+      <c r="F11" s="3">
+        <v>18</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>6</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>53</v>
       </c>
@@ -1550,14 +1858,23 @@
       <c r="E12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="4">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" customHeight="1">
+      <c r="F12" s="3">
+        <v>12</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H12" s="3">
+        <v>6</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>54</v>
       </c>
@@ -1573,14 +1890,23 @@
       <c r="E13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="4">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" customHeight="1">
+      <c r="F13" s="3">
+        <v>12</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3">
+        <v>6</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>232</v>
       </c>
@@ -1596,14 +1922,23 @@
       <c r="E14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="4">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4">
+      <c r="F14" s="3">
+        <v>24</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3">
+        <v>24</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
+      <c r="J14" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15" customHeight="1">
+    <row r="15" spans="1:10" ht="15" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>233</v>
       </c>
@@ -1619,14 +1954,23 @@
       <c r="E15" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" customHeight="1">
+      <c r="F15" s="3">
+        <v>6</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H15" s="3">
+        <v>6</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>234</v>
       </c>
@@ -1642,14 +1986,23 @@
       <c r="E16" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F16" s="4">
-        <v>1</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1">
+      <c r="F16" s="3">
+        <v>18</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3">
+        <v>24</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>235</v>
       </c>
@@ -1665,14 +2018,23 @@
       <c r="E17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="4">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1">
+      <c r="F17" s="3">
+        <v>12</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H17" s="3">
+        <v>6</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="15" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>236</v>
       </c>
@@ -1688,14 +2050,23 @@
       <c r="E18" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="F18" s="4">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4">
+      <c r="F18" s="3">
+        <v>12</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H18" s="3">
+        <v>6</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
+      <c r="J18" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1">
+    <row r="19" spans="1:14" ht="15" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>237</v>
       </c>
@@ -1711,14 +2082,23 @@
       <c r="E19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="4">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1">
+      <c r="F19" s="3">
+        <v>24</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3">
+        <v>6</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>238</v>
       </c>
@@ -1734,14 +2114,23 @@
       <c r="E20" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F20" s="4">
-        <v>1</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1">
+      <c r="F20" s="3">
+        <v>6</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H20" s="3">
+        <v>24</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>239</v>
       </c>
@@ -1757,14 +2146,23 @@
       <c r="E21" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="F21" s="4">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1">
+      <c r="F21" s="3">
+        <v>18</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3">
+        <v>6</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>240</v>
       </c>
@@ -1780,15 +2178,24 @@
       <c r="E22" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="F22" s="4">
-        <v>1</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K22" s="7"/>
-    </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1">
+      <c r="F22" s="3">
+        <v>12</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1</v>
+      </c>
+      <c r="H22" s="3">
+        <v>6</v>
+      </c>
+      <c r="I22" s="4">
+        <v>1</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N22" s="7"/>
+    </row>
+    <row r="23" spans="1:14" ht="15" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>241</v>
       </c>
@@ -1804,14 +2211,23 @@
       <c r="E23" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="F23" s="4">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1">
+      <c r="F23" s="3">
+        <v>12</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H23" s="3">
+        <v>24</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>242</v>
       </c>
@@ -1827,14 +2243,23 @@
       <c r="E24" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F24" s="4">
-        <v>1</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1">
+      <c r="F24" s="3">
+        <v>24</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1</v>
+      </c>
+      <c r="H24" s="3">
+        <v>24</v>
+      </c>
+      <c r="I24" s="4">
+        <v>1</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="15" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>243</v>
       </c>
@@ -1850,14 +2275,23 @@
       <c r="E25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F25" s="4">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="15" customHeight="1">
+      <c r="F25" s="3">
+        <v>6</v>
+      </c>
+      <c r="G25" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H25" s="3">
+        <v>6</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>55</v>
       </c>
@@ -1873,14 +2307,23 @@
       <c r="E26" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F26" s="4">
-        <v>1</v>
-      </c>
-      <c r="G26" s="4">
+      <c r="F26" s="3">
+        <v>18</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H26" s="3">
+        <v>24</v>
+      </c>
+      <c r="I26" s="4">
+        <v>1</v>
+      </c>
+      <c r="J26" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1">
+    <row r="27" spans="1:14" ht="15" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>59</v>
       </c>
@@ -1896,14 +2339,23 @@
       <c r="E27" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="4">
-        <v>0</v>
-      </c>
-      <c r="G27" s="4">
+      <c r="F27" s="3">
+        <v>12</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1</v>
+      </c>
+      <c r="H27" s="3">
+        <v>6</v>
+      </c>
+      <c r="I27" s="4">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15" customHeight="1">
+    <row r="28" spans="1:14" ht="15" customHeight="1">
       <c r="A28" s="2" t="s">
         <v>62</v>
       </c>
@@ -1919,15 +2371,24 @@
       <c r="E28" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F28" s="4">
-        <v>1</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K28" s="7"/>
-    </row>
-    <row r="29" spans="1:11" ht="15" customHeight="1">
+      <c r="F28" s="3">
+        <v>12</v>
+      </c>
+      <c r="G28" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H28" s="3">
+        <v>24</v>
+      </c>
+      <c r="I28" s="4">
+        <v>1</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N28" s="7"/>
+    </row>
+    <row r="29" spans="1:14" ht="15" customHeight="1">
       <c r="A29" s="2" t="s">
         <v>64</v>
       </c>
@@ -1943,14 +2404,23 @@
       <c r="E29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F29" s="4">
-        <v>0</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="15" customHeight="1">
+      <c r="F29" s="3">
+        <v>24</v>
+      </c>
+      <c r="G29" s="3">
+        <v>1</v>
+      </c>
+      <c r="H29" s="3">
+        <v>6</v>
+      </c>
+      <c r="I29" s="4">
+        <v>0</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="2" t="s">
         <v>66</v>
       </c>
@@ -1966,14 +2436,23 @@
       <c r="E30" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F30" s="4">
-        <v>1</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="15" customHeight="1">
+      <c r="F30" s="3">
+        <v>6</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1</v>
+      </c>
+      <c r="H30" s="3">
+        <v>6</v>
+      </c>
+      <c r="I30" s="4">
+        <v>1</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="2" t="s">
         <v>69</v>
       </c>
@@ -1989,14 +2468,23 @@
       <c r="E31" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F31" s="4">
-        <v>0</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="15" customHeight="1">
+      <c r="F31" s="3">
+        <v>18</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H31" s="3">
+        <v>24</v>
+      </c>
+      <c r="I31" s="4">
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="2" t="s">
         <v>72</v>
       </c>
@@ -2012,14 +2500,23 @@
       <c r="E32" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="4">
-        <v>1</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15" customHeight="1">
+      <c r="F32" s="3">
+        <v>12</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3">
+        <v>6</v>
+      </c>
+      <c r="I32" s="4">
+        <v>1</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1">
       <c r="A33" s="2" t="s">
         <v>75</v>
       </c>
@@ -2035,14 +2532,23 @@
       <c r="E33" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F33" s="4">
-        <v>0</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1">
+      <c r="F33" s="3">
+        <v>12</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H33" s="3">
+        <v>24</v>
+      </c>
+      <c r="I33" s="4">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1">
       <c r="A34" s="2" t="s">
         <v>78</v>
       </c>
@@ -2058,14 +2564,23 @@
       <c r="E34" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F34" s="4">
-        <v>1</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1">
+      <c r="F34" s="3">
+        <v>24</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H34" s="3">
+        <v>6</v>
+      </c>
+      <c r="I34" s="4">
+        <v>1</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1">
       <c r="A35" s="2" t="s">
         <v>80</v>
       </c>
@@ -2081,14 +2596,23 @@
       <c r="E35" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F35" s="4">
-        <v>0</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15" customHeight="1">
+      <c r="F35" s="3">
+        <v>6</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1</v>
+      </c>
+      <c r="H35" s="3">
+        <v>24</v>
+      </c>
+      <c r="I35" s="4">
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1">
       <c r="A36" s="2" t="s">
         <v>82</v>
       </c>
@@ -2104,14 +2628,23 @@
       <c r="E36" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F36" s="4">
-        <v>1</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15" customHeight="1">
+      <c r="F36" s="3">
+        <v>18</v>
+      </c>
+      <c r="G36" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H36" s="3">
+        <v>6</v>
+      </c>
+      <c r="I36" s="4">
+        <v>1</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1">
       <c r="A37" s="2" t="s">
         <v>84</v>
       </c>
@@ -2127,14 +2660,23 @@
       <c r="E37" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F37" s="4">
-        <v>0</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="15" customHeight="1">
+      <c r="F37" s="3">
+        <v>12</v>
+      </c>
+      <c r="G37" s="3">
+        <v>1</v>
+      </c>
+      <c r="H37" s="3">
+        <v>24</v>
+      </c>
+      <c r="I37" s="4">
+        <v>0</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1">
       <c r="A38" s="2" t="s">
         <v>219</v>
       </c>
@@ -2150,14 +2692,23 @@
       <c r="E38" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F38" s="4">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4">
+      <c r="F38" s="3">
+        <v>12</v>
+      </c>
+      <c r="G38" s="3">
+        <v>1</v>
+      </c>
+      <c r="H38" s="3">
+        <v>6</v>
+      </c>
+      <c r="I38" s="4">
+        <v>1</v>
+      </c>
+      <c r="J38" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15" customHeight="1">
+    <row r="39" spans="1:10" ht="15" customHeight="1">
       <c r="A39" s="2" t="s">
         <v>220</v>
       </c>
@@ -2173,14 +2724,23 @@
       <c r="E39" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F39" s="4">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="15" customHeight="1">
+      <c r="F39" s="3">
+        <v>24</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H39" s="3">
+        <v>24</v>
+      </c>
+      <c r="I39" s="4">
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15" customHeight="1">
       <c r="A40" s="2" t="s">
         <v>221</v>
       </c>
@@ -2196,14 +2756,23 @@
       <c r="E40" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F40" s="4">
-        <v>1</v>
-      </c>
-      <c r="G40" s="4">
+      <c r="F40" s="3">
+        <v>6</v>
+      </c>
+      <c r="G40" s="3">
+        <v>1</v>
+      </c>
+      <c r="H40" s="3">
+        <v>6</v>
+      </c>
+      <c r="I40" s="4">
+        <v>1</v>
+      </c>
+      <c r="J40" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15" customHeight="1">
+    <row r="41" spans="1:10" ht="15" customHeight="1">
       <c r="A41" s="2" t="s">
         <v>222</v>
       </c>
@@ -2219,14 +2788,23 @@
       <c r="E41" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F41" s="4">
-        <v>0</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15" customHeight="1">
+      <c r="F41" s="3">
+        <v>18</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H41" s="3">
+        <v>6</v>
+      </c>
+      <c r="I41" s="4">
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15" customHeight="1">
       <c r="A42" s="2" t="s">
         <v>223</v>
       </c>
@@ -2242,14 +2820,23 @@
       <c r="E42" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F42" s="4">
-        <v>1</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15" customHeight="1">
+      <c r="F42" s="3">
+        <v>12</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H42" s="3">
+        <v>24</v>
+      </c>
+      <c r="I42" s="4">
+        <v>1</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15" customHeight="1">
       <c r="A43" s="2" t="s">
         <v>224</v>
       </c>
@@ -2265,14 +2852,23 @@
       <c r="E43" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F43" s="4">
-        <v>0</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15" customHeight="1">
+      <c r="F43" s="3">
+        <v>12</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1</v>
+      </c>
+      <c r="H43" s="3">
+        <v>6</v>
+      </c>
+      <c r="I43" s="4">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15" customHeight="1">
       <c r="A44" s="2" t="s">
         <v>225</v>
       </c>
@@ -2288,14 +2884,23 @@
       <c r="E44" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F44" s="4">
-        <v>1</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15" customHeight="1">
+      <c r="F44" s="3">
+        <v>24</v>
+      </c>
+      <c r="G44" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H44" s="3">
+        <v>24</v>
+      </c>
+      <c r="I44" s="4">
+        <v>1</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15" customHeight="1">
       <c r="A45" s="2" t="s">
         <v>226</v>
       </c>
@@ -2311,14 +2916,23 @@
       <c r="E45" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="F45" s="4">
-        <v>0</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1">
+      <c r="F45" s="3">
+        <v>6</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1</v>
+      </c>
+      <c r="H45" s="3">
+        <v>6</v>
+      </c>
+      <c r="I45" s="4">
+        <v>0</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15" customHeight="1">
       <c r="A46" s="2" t="s">
         <v>227</v>
       </c>
@@ -2334,14 +2948,23 @@
       <c r="E46" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="F46" s="4">
-        <v>1</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15" customHeight="1">
+      <c r="F46" s="3">
+        <v>18</v>
+      </c>
+      <c r="G46" s="3">
+        <v>1</v>
+      </c>
+      <c r="H46" s="3">
+        <v>6</v>
+      </c>
+      <c r="I46" s="4">
+        <v>1</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15" customHeight="1">
       <c r="A47" s="2" t="s">
         <v>228</v>
       </c>
@@ -2357,14 +2980,23 @@
       <c r="E47" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="F47" s="4">
-        <v>0</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1">
+      <c r="F47" s="3">
+        <v>12</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H47" s="3">
+        <v>6</v>
+      </c>
+      <c r="I47" s="4">
+        <v>0</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="15" customHeight="1">
       <c r="A48" s="2" t="s">
         <v>229</v>
       </c>
@@ -2380,14 +3012,23 @@
       <c r="E48" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F48" s="4">
-        <v>1</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="15" customHeight="1">
+      <c r="F48" s="3">
+        <v>12</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1</v>
+      </c>
+      <c r="H48" s="3">
+        <v>6</v>
+      </c>
+      <c r="I48" s="4">
+        <v>1</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="15" customHeight="1">
       <c r="A49" s="2" t="s">
         <v>230</v>
       </c>
@@ -2403,14 +3044,23 @@
       <c r="E49" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F49" s="4">
-        <v>0</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="15" customHeight="1">
+      <c r="F49" s="3">
+        <v>24</v>
+      </c>
+      <c r="G49" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H49" s="3">
+        <v>24</v>
+      </c>
+      <c r="I49" s="4">
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="15" customHeight="1">
       <c r="A50" s="2" t="s">
         <v>104</v>
       </c>
@@ -2426,14 +3076,23 @@
       <c r="E50" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F50" s="4">
-        <v>1</v>
-      </c>
-      <c r="G50" s="4">
+      <c r="F50" s="3">
+        <v>6</v>
+      </c>
+      <c r="G50" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H50" s="3">
+        <v>6</v>
+      </c>
+      <c r="I50" s="4">
+        <v>1</v>
+      </c>
+      <c r="J50" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15" customHeight="1">
+    <row r="51" spans="1:10" ht="15" customHeight="1">
       <c r="A51" s="2" t="s">
         <v>107</v>
       </c>
@@ -2449,14 +3108,23 @@
       <c r="E51" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F51" s="4">
-        <v>0</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="15" customHeight="1">
+      <c r="F51" s="3">
+        <v>18</v>
+      </c>
+      <c r="G51" s="3">
+        <v>1</v>
+      </c>
+      <c r="H51" s="3">
+        <v>6</v>
+      </c>
+      <c r="I51" s="4">
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="15" customHeight="1">
       <c r="A52" s="2" t="s">
         <v>110</v>
       </c>
@@ -2472,14 +3140,23 @@
       <c r="E52" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F52" s="4">
-        <v>1</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="15" customHeight="1">
+      <c r="F52" s="3">
+        <v>12</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H52" s="3">
+        <v>6</v>
+      </c>
+      <c r="I52" s="4">
+        <v>1</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="15" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>113</v>
       </c>
@@ -2495,14 +3172,23 @@
       <c r="E53" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F53" s="4">
-        <v>0</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="15" customHeight="1">
+      <c r="F53" s="3">
+        <v>12</v>
+      </c>
+      <c r="G53" s="3">
+        <v>1</v>
+      </c>
+      <c r="H53" s="3">
+        <v>6</v>
+      </c>
+      <c r="I53" s="4">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="15" customHeight="1">
       <c r="A54" s="2" t="s">
         <v>116</v>
       </c>
@@ -2518,14 +3204,23 @@
       <c r="E54" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F54" s="4">
-        <v>1</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="15" customHeight="1">
+      <c r="F54" s="3">
+        <v>24</v>
+      </c>
+      <c r="G54" s="3">
+        <v>1</v>
+      </c>
+      <c r="H54" s="3">
+        <v>6</v>
+      </c>
+      <c r="I54" s="4">
+        <v>1</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="15" customHeight="1">
       <c r="A55" s="2" t="s">
         <v>118</v>
       </c>
@@ -2541,14 +3236,23 @@
       <c r="E55" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F55" s="4">
-        <v>0</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="15" customHeight="1">
+      <c r="F55" s="3">
+        <v>6</v>
+      </c>
+      <c r="G55" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H55" s="3">
+        <v>24</v>
+      </c>
+      <c r="I55" s="4">
+        <v>0</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="15" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>121</v>
       </c>
@@ -2564,14 +3268,23 @@
       <c r="E56" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F56" s="4">
-        <v>1</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="15" customHeight="1">
+      <c r="F56" s="3">
+        <v>18</v>
+      </c>
+      <c r="G56" s="3">
+        <v>1</v>
+      </c>
+      <c r="H56" s="3">
+        <v>6</v>
+      </c>
+      <c r="I56" s="4">
+        <v>1</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="15" customHeight="1">
       <c r="A57" s="2" t="s">
         <v>124</v>
       </c>
@@ -2587,14 +3300,23 @@
       <c r="E57" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F57" s="4">
-        <v>0</v>
-      </c>
-      <c r="G57" s="4">
+      <c r="F57" s="3">
+        <v>12</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H57" s="3">
+        <v>6</v>
+      </c>
+      <c r="I57" s="4">
+        <v>0</v>
+      </c>
+      <c r="J57" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15" customHeight="1">
+    <row r="58" spans="1:10" ht="15" customHeight="1">
       <c r="A58" s="2" t="s">
         <v>127</v>
       </c>
@@ -2610,14 +3332,23 @@
       <c r="E58" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F58" s="4">
-        <v>1</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15" customHeight="1">
+      <c r="F58" s="3">
+        <v>12</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H58" s="3">
+        <v>24</v>
+      </c>
+      <c r="I58" s="4">
+        <v>1</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="15" customHeight="1">
       <c r="A59" s="2" t="s">
         <v>129</v>
       </c>
@@ -2633,14 +3364,23 @@
       <c r="E59" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F59" s="4">
-        <v>0</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15" customHeight="1">
+      <c r="F59" s="3">
+        <v>24</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1</v>
+      </c>
+      <c r="H59" s="3">
+        <v>6</v>
+      </c>
+      <c r="I59" s="4">
+        <v>0</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="15" customHeight="1">
       <c r="A60" s="2" t="s">
         <v>131</v>
       </c>
@@ -2656,14 +3396,23 @@
       <c r="E60" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F60" s="4">
-        <v>1</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="15" customHeight="1">
+      <c r="F60" s="3">
+        <v>6</v>
+      </c>
+      <c r="G60" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H60" s="3">
+        <v>6</v>
+      </c>
+      <c r="I60" s="4">
+        <v>1</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="15" customHeight="1">
       <c r="A61" s="2" t="s">
         <v>134</v>
       </c>
@@ -2679,14 +3428,23 @@
       <c r="E61" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F61" s="4">
-        <v>0</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="15" customHeight="1">
+      <c r="F61" s="3">
+        <v>18</v>
+      </c>
+      <c r="G61" s="3">
+        <v>1</v>
+      </c>
+      <c r="H61" s="3">
+        <v>6</v>
+      </c>
+      <c r="I61" s="4">
+        <v>0</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="15" customHeight="1">
       <c r="A62" s="2" t="s">
         <v>137</v>
       </c>
@@ -2702,14 +3460,23 @@
       <c r="E62" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F62" s="4">
-        <v>1</v>
-      </c>
-      <c r="G62" s="4">
+      <c r="F62" s="3">
+        <v>12</v>
+      </c>
+      <c r="G62" s="3">
+        <v>1</v>
+      </c>
+      <c r="H62" s="3">
+        <v>24</v>
+      </c>
+      <c r="I62" s="4">
+        <v>1</v>
+      </c>
+      <c r="J62" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15" customHeight="1">
+    <row r="63" spans="1:10" ht="15" customHeight="1">
       <c r="A63" s="2" t="s">
         <v>141</v>
       </c>
@@ -2725,14 +3492,23 @@
       <c r="E63" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F63" s="4">
-        <v>0</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="15" customHeight="1">
+      <c r="F63" s="3">
+        <v>12</v>
+      </c>
+      <c r="G63" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H63" s="3">
+        <v>6</v>
+      </c>
+      <c r="I63" s="4">
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="15" customHeight="1">
       <c r="A64" s="2" t="s">
         <v>144</v>
       </c>
@@ -2748,14 +3524,23 @@
       <c r="E64" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F64" s="4">
-        <v>1</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="15" customHeight="1">
+      <c r="F64" s="3">
+        <v>24</v>
+      </c>
+      <c r="G64" s="3">
+        <v>1</v>
+      </c>
+      <c r="H64" s="3">
+        <v>24</v>
+      </c>
+      <c r="I64" s="4">
+        <v>1</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="15" customHeight="1">
       <c r="A65" s="2" t="s">
         <v>147</v>
       </c>
@@ -2771,14 +3556,23 @@
       <c r="E65" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F65" s="4">
-        <v>0</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="15" customHeight="1">
+      <c r="F65" s="3">
+        <v>6</v>
+      </c>
+      <c r="G65" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H65" s="3">
+        <v>6</v>
+      </c>
+      <c r="I65" s="4">
+        <v>0</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="15" customHeight="1">
       <c r="A66" s="2" t="s">
         <v>150</v>
       </c>
@@ -2794,14 +3588,23 @@
       <c r="E66" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F66" s="4">
-        <v>1</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="15" customHeight="1">
+      <c r="F66" s="3">
+        <v>18</v>
+      </c>
+      <c r="G66" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H66" s="3">
+        <v>24</v>
+      </c>
+      <c r="I66" s="4">
+        <v>1</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="15" customHeight="1">
       <c r="A67" s="2" t="s">
         <v>153</v>
       </c>
@@ -2817,14 +3620,23 @@
       <c r="E67" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F67" s="4">
-        <v>0</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="15" customHeight="1">
+      <c r="F67" s="3">
+        <v>12</v>
+      </c>
+      <c r="G67" s="3">
+        <v>1</v>
+      </c>
+      <c r="H67" s="3">
+        <v>6</v>
+      </c>
+      <c r="I67" s="4">
+        <v>0</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="15" customHeight="1">
       <c r="A68" s="2" t="s">
         <v>155</v>
       </c>
@@ -2840,14 +3652,23 @@
       <c r="E68" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F68" s="4">
-        <v>1</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="15" customHeight="1">
+      <c r="F68" s="3">
+        <v>12</v>
+      </c>
+      <c r="G68" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H68" s="3">
+        <v>6</v>
+      </c>
+      <c r="I68" s="4">
+        <v>1</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="15" customHeight="1">
       <c r="A69" s="2" t="s">
         <v>158</v>
       </c>
@@ -2863,14 +3684,23 @@
       <c r="E69" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F69" s="4">
-        <v>0</v>
-      </c>
-      <c r="G69" s="4">
+      <c r="F69" s="3">
+        <v>24</v>
+      </c>
+      <c r="G69" s="3">
+        <v>1</v>
+      </c>
+      <c r="H69" s="3">
+        <v>24</v>
+      </c>
+      <c r="I69" s="4">
+        <v>0</v>
+      </c>
+      <c r="J69" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15" customHeight="1">
+    <row r="70" spans="1:10" ht="15" customHeight="1">
       <c r="A70" s="2" t="s">
         <v>161</v>
       </c>
@@ -2886,14 +3716,23 @@
       <c r="E70" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F70" s="4">
-        <v>1</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="15" customHeight="1">
+      <c r="F70" s="3">
+        <v>6</v>
+      </c>
+      <c r="G70" s="3">
+        <v>1</v>
+      </c>
+      <c r="H70" s="3">
+        <v>6</v>
+      </c>
+      <c r="I70" s="4">
+        <v>1</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="15" customHeight="1">
       <c r="A71" s="2" t="s">
         <v>164</v>
       </c>
@@ -2909,14 +3748,23 @@
       <c r="E71" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F71" s="4">
-        <v>0</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="15" customHeight="1">
+      <c r="F71" s="3">
+        <v>18</v>
+      </c>
+      <c r="G71" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H71" s="3">
+        <v>24</v>
+      </c>
+      <c r="I71" s="4">
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="15" customHeight="1">
       <c r="A72" s="2" t="s">
         <v>166</v>
       </c>
@@ -2932,14 +3780,23 @@
       <c r="E72" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F72" s="4">
-        <v>1</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="15" customHeight="1">
+      <c r="F72" s="3">
+        <v>12</v>
+      </c>
+      <c r="G72" s="3">
+        <v>1</v>
+      </c>
+      <c r="H72" s="3">
+        <v>6</v>
+      </c>
+      <c r="I72" s="4">
+        <v>1</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="15" customHeight="1">
       <c r="A73" s="2" t="s">
         <v>168</v>
       </c>
@@ -2955,14 +3812,23 @@
       <c r="E73" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F73" s="4">
-        <v>0</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="15" customHeight="1">
+      <c r="F73" s="3">
+        <v>12</v>
+      </c>
+      <c r="G73" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H73" s="3">
+        <v>6</v>
+      </c>
+      <c r="I73" s="4">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="15" customHeight="1">
       <c r="A74" s="2" t="s">
         <v>171</v>
       </c>
@@ -2978,14 +3844,23 @@
       <c r="E74" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F74" s="4">
-        <v>1</v>
-      </c>
-      <c r="G74" s="4">
+      <c r="F74" s="3">
+        <v>24</v>
+      </c>
+      <c r="G74" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H74" s="3">
+        <v>24</v>
+      </c>
+      <c r="I74" s="4">
+        <v>1</v>
+      </c>
+      <c r="J74" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15" customHeight="1">
+    <row r="75" spans="1:10" ht="15" customHeight="1">
       <c r="A75" s="2" t="s">
         <v>175</v>
       </c>
@@ -3001,14 +3876,23 @@
       <c r="E75" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F75" s="4">
-        <v>0</v>
-      </c>
-      <c r="G75" s="4">
+      <c r="F75" s="3">
+        <v>6</v>
+      </c>
+      <c r="G75" s="3">
+        <v>1</v>
+      </c>
+      <c r="H75" s="3">
+        <v>6</v>
+      </c>
+      <c r="I75" s="4">
+        <v>0</v>
+      </c>
+      <c r="J75" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15" customHeight="1">
+    <row r="76" spans="1:10" ht="15" customHeight="1">
       <c r="A76" s="2" t="s">
         <v>177</v>
       </c>
@@ -3024,14 +3908,23 @@
       <c r="E76" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F76" s="4">
-        <v>1</v>
-      </c>
-      <c r="G76" s="4">
+      <c r="F76" s="3">
+        <v>18</v>
+      </c>
+      <c r="G76" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H76" s="3">
+        <v>6</v>
+      </c>
+      <c r="I76" s="4">
+        <v>1</v>
+      </c>
+      <c r="J76" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15" customHeight="1">
+    <row r="77" spans="1:10" ht="15" customHeight="1">
       <c r="A77" s="2" t="s">
         <v>179</v>
       </c>
@@ -3047,14 +3940,23 @@
       <c r="E77" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F77" s="4">
-        <v>0</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="15" customHeight="1">
+      <c r="F77" s="3">
+        <v>12</v>
+      </c>
+      <c r="G77" s="3">
+        <v>1</v>
+      </c>
+      <c r="H77" s="3">
+        <v>24</v>
+      </c>
+      <c r="I77" s="4">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="15" customHeight="1">
       <c r="A78" s="2" t="s">
         <v>182</v>
       </c>
@@ -3070,14 +3972,23 @@
       <c r="E78" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F78" s="4">
-        <v>1</v>
-      </c>
-      <c r="G78" s="4">
+      <c r="F78" s="3">
+        <v>12</v>
+      </c>
+      <c r="G78" s="3">
+        <v>1</v>
+      </c>
+      <c r="H78" s="3">
+        <v>6</v>
+      </c>
+      <c r="I78" s="4">
+        <v>1</v>
+      </c>
+      <c r="J78" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15" customHeight="1">
+    <row r="79" spans="1:10" ht="15" customHeight="1">
       <c r="A79" s="2" t="s">
         <v>184</v>
       </c>
@@ -3093,14 +4004,23 @@
       <c r="E79" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F79" s="4">
-        <v>0</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="15" customHeight="1">
+      <c r="F79" s="3">
+        <v>24</v>
+      </c>
+      <c r="G79" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="H79" s="3">
+        <v>6</v>
+      </c>
+      <c r="I79" s="4">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="15" customHeight="1">
       <c r="A80" s="2" t="s">
         <v>186</v>
       </c>
@@ -3116,14 +4036,23 @@
       <c r="E80" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F80" s="4">
-        <v>1</v>
-      </c>
-      <c r="G80" s="4">
+      <c r="F80" s="3">
+        <v>6</v>
+      </c>
+      <c r="G80" s="3">
+        <v>1</v>
+      </c>
+      <c r="H80" s="3">
+        <v>24</v>
+      </c>
+      <c r="I80" s="4">
+        <v>1</v>
+      </c>
+      <c r="J80" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15" customHeight="1">
+    <row r="81" spans="1:10" ht="15" customHeight="1">
       <c r="A81" s="2" t="s">
         <v>188</v>
       </c>
@@ -3139,14 +4068,23 @@
       <c r="E81" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F81" s="4">
-        <v>0</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="15" customHeight="1">
+      <c r="F81" s="3">
+        <v>18</v>
+      </c>
+      <c r="G81" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H81" s="3">
+        <v>6</v>
+      </c>
+      <c r="I81" s="4">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="15" customHeight="1">
       <c r="A82" s="2" t="s">
         <v>191</v>
       </c>
@@ -3162,14 +4100,23 @@
       <c r="E82" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="F82" s="4">
-        <v>1</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="15" customHeight="1">
+      <c r="F82" s="3">
+        <v>12</v>
+      </c>
+      <c r="G82" s="3">
+        <v>1</v>
+      </c>
+      <c r="H82" s="3">
+        <v>6</v>
+      </c>
+      <c r="I82" s="4">
+        <v>1</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="15" customHeight="1">
       <c r="A83" s="2" t="s">
         <v>193</v>
       </c>
@@ -3185,14 +4132,23 @@
       <c r="E83" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="F83" s="4">
-        <v>0</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="15" customHeight="1">
+      <c r="F83" s="3">
+        <v>24</v>
+      </c>
+      <c r="G83" s="3">
+        <v>1</v>
+      </c>
+      <c r="H83" s="3">
+        <v>6</v>
+      </c>
+      <c r="I83" s="4">
+        <v>0</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="15" customHeight="1">
       <c r="A84" s="2" t="s">
         <v>196</v>
       </c>
@@ -3208,14 +4164,23 @@
       <c r="E84" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F84" s="4">
-        <v>1</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="15" customHeight="1">
+      <c r="F84" s="3">
+        <v>6</v>
+      </c>
+      <c r="G84" s="3">
+        <v>1</v>
+      </c>
+      <c r="H84" s="3">
+        <v>24</v>
+      </c>
+      <c r="I84" s="4">
+        <v>1</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="15" customHeight="1">
       <c r="A85" s="2" t="s">
         <v>197</v>
       </c>
@@ -3231,10 +4196,19 @@
       <c r="E85" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F85" s="4">
-        <v>0</v>
-      </c>
-      <c r="G85" s="4" t="s">
+      <c r="F85" s="3">
+        <v>18</v>
+      </c>
+      <c r="G85" s="3">
+        <v>1</v>
+      </c>
+      <c r="H85" s="3">
+        <v>6</v>
+      </c>
+      <c r="I85" s="4">
+        <v>0</v>
+      </c>
+      <c r="J85" s="4" t="s">
         <v>13</v>
       </c>
     </row>

--- a/config/Excel/NPC.xlsx
+++ b/config/Excel/NPC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880CFE41-DE21-4658-957B-59AC0224A766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B09C09-34B5-459D-AE4D-B98DCF1825D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1273,8 +1273,8 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="屬性"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="外觀"/>
     <tableColumn id="10" xr3:uid="{6F874BA1-FF6B-4646-B1EE-72FFC55222C6}" name="移動速度(米/秒)" dataDxfId="2" dataCellStyle="Normal"/>
-    <tableColumn id="9" xr3:uid="{E04420AF-891B-480A-9ED8-4D87846DE54E}" name="攻擊速度(次/秒)" dataDxfId="0" dataCellStyle="Normal"/>
-    <tableColumn id="8" xr3:uid="{4BEE5E3D-977E-470C-BC00-4A996DB00A9E}" name="攻擊距離(米)" dataDxfId="1" dataCellStyle="Normal"/>
+    <tableColumn id="9" xr3:uid="{E04420AF-891B-480A-9ED8-4D87846DE54E}" name="攻擊速度(次/秒)" dataDxfId="1" dataCellStyle="Normal"/>
+    <tableColumn id="8" xr3:uid="{4BEE5E3D-977E-470C-BC00-4A996DB00A9E}" name="攻擊距離(米)" dataDxfId="0" dataCellStyle="Normal"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="魔法型（1是／0否）"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="出現權重"/>
   </tableColumns>
@@ -1897,7 +1897,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="3">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I13" s="4">
         <v>0</v>
@@ -2089,7 +2089,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="3">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I19" s="4">
         <v>0</v>
@@ -2443,7 +2443,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="3">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I30" s="4">
         <v>1</v>
@@ -2635,7 +2635,7 @@
         <v>1.5</v>
       </c>
       <c r="H36" s="3">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I36" s="4">
         <v>1</v>
@@ -2987,7 +2987,7 @@
         <v>0.75</v>
       </c>
       <c r="H47" s="3">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I47" s="4">
         <v>0</v>
@@ -3147,7 +3147,7 @@
         <v>1.5</v>
       </c>
       <c r="H52" s="3">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I52" s="4">
         <v>1</v>
@@ -3403,7 +3403,7 @@
         <v>1.5</v>
       </c>
       <c r="H60" s="3">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I60" s="4">
         <v>1</v>
@@ -3819,7 +3819,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" s="3">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I73" s="4">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="3">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I78" s="4">
         <v>1</v>
@@ -4107,7 +4107,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="3">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I82" s="4">
         <v>1</v>

--- a/config/Excel/NPC.xlsx
+++ b/config/Excel/NPC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C391DA-CCC0-49C7-A517-283D4A20BF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA29BDE7-9646-42A7-9F72-3939C3C4ABC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2139,12 +2139,6 @@
     <t>🕷️</t>
   </si>
   <si>
-    <t>e_poisonspit;e_splitter</t>
-  </si>
-  <si>
-    <t>封魔塔BOSS｜專屬：劇毒吐息（吐出數團毒液，命中的目標會中毒。）；分裂（死亡時分裂成數隻較弱的分身。）｜隨機：從隨機技能池抽 4~6 個</t>
-  </si>
-  <si>
     <t>tower_boss_6</t>
   </si>
   <si>
@@ -2215,6 +2209,14 @@
   </si>
   <si>
     <t>封魔塔BOSS｜專屬：衰弱詛咒（詛咒你，使你的攻擊力與防禦力降低一段時間。）；魔力吸取（抽走你一部分法力，並用來治療自己。）｜隨機：從隨機技能池抽 4~6 個</t>
+  </si>
+  <si>
+    <t>e_poisonspit;e_vampiric</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>封魔塔BOSS｜專屬：劇毒吐息（吐出數團毒液，命中的目標會中毒。）；嗜血（每次擊中你都會把造成傷害的一部分吸成自己的生命。）｜隨機：從隨機技能池抽 4~6 個</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -18510,7 +18512,7 @@
         <v>13</v>
       </c>
       <c r="L342" s="22" t="s">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c r="M342" s="22" t="s">
         <v>580</v>
@@ -18519,15 +18521,15 @@
         <v>297</v>
       </c>
       <c r="O342" s="22" t="s">
-        <v>599</v>
+        <v>623</v>
       </c>
     </row>
     <row r="343" spans="1:15">
       <c r="A343" s="15" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B343" s="15" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C343" s="15" t="s">
         <v>577</v>
@@ -18539,7 +18541,7 @@
         <v>11</v>
       </c>
       <c r="F343" s="15" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G343" s="13"/>
       <c r="H343" s="13"/>
@@ -18548,7 +18550,7 @@
         <v>13</v>
       </c>
       <c r="L343" s="22" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="M343" s="22" t="s">
         <v>580</v>
@@ -18557,15 +18559,15 @@
         <v>297</v>
       </c>
       <c r="O343" s="22" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="344" spans="1:15">
       <c r="A344" s="15" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B344" s="15" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C344" s="15" t="s">
         <v>577</v>
@@ -18586,7 +18588,7 @@
         <v>13</v>
       </c>
       <c r="L344" s="22" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="M344" s="22" t="s">
         <v>580</v>
@@ -18595,15 +18597,15 @@
         <v>297</v>
       </c>
       <c r="O344" s="22" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="345" spans="1:15">
       <c r="A345" s="15" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B345" s="15" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C345" s="15" t="s">
         <v>577</v>
@@ -18615,7 +18617,7 @@
         <v>30</v>
       </c>
       <c r="F345" s="15" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G345" s="13"/>
       <c r="H345" s="13"/>
@@ -18624,7 +18626,7 @@
         <v>13</v>
       </c>
       <c r="L345" s="22" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="M345" s="22" t="s">
         <v>580</v>
@@ -18633,15 +18635,15 @@
         <v>297</v>
       </c>
       <c r="O345" s="22" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="346" spans="1:15">
       <c r="A346" s="15" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B346" s="15" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C346" s="15" t="s">
         <v>577</v>
@@ -18653,7 +18655,7 @@
         <v>35</v>
       </c>
       <c r="F346" s="15" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="G346" s="13"/>
       <c r="H346" s="13"/>
@@ -18662,7 +18664,7 @@
         <v>13</v>
       </c>
       <c r="L346" s="22" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="M346" s="22" t="s">
         <v>580</v>
@@ -18671,15 +18673,15 @@
         <v>297</v>
       </c>
       <c r="O346" s="22" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="347" spans="1:15">
       <c r="A347" s="15" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B347" s="15" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C347" s="15" t="s">
         <v>577</v>
@@ -18691,7 +18693,7 @@
         <v>11</v>
       </c>
       <c r="F347" s="15" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G347" s="13"/>
       <c r="H347" s="13"/>
@@ -18700,7 +18702,7 @@
         <v>13</v>
       </c>
       <c r="L347" s="22" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="M347" s="22" t="s">
         <v>580</v>
@@ -18709,7 +18711,7 @@
         <v>297</v>
       </c>
       <c r="O347" s="22" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/NPC.xlsx
+++ b/config/Excel/NPC.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D603DE9-4611-4DFE-B750-31DFA1D928C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E48158-F07C-4CEB-9862-EFBD8AAA11AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3015" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NPC" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8977" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8977" uniqueCount="976">
   <si>
     <t>NPC識別碼</t>
   </si>
@@ -3505,6 +3505,10 @@
   </si>
   <si>
     <t>縮放比</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3658,7 +3662,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3747,6 +3751,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4165,6 +4172,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NPCTable" displayName="NPCTable" ref="A1:V491" totalsRowShown="0">
+  <autoFilter ref="A1:V491" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="NPC識別碼"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="NPC名稱"/>
@@ -4389,23 +4397,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V491"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="11" width="22.625" style="15" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="15" customWidth="1"/>
+    <col min="7" max="11" width="22.59765625" style="15" customWidth="1"/>
+    <col min="12" max="12" width="10.59765625" style="15" customWidth="1"/>
     <col min="13" max="14" width="16" customWidth="1"/>
     <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="16" width="19.625" style="15" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="20" max="20" width="12.25" customWidth="1"/>
+    <col min="16" max="16" width="19.59765625" style="15" customWidth="1"/>
+    <col min="17" max="17" width="22.19921875" customWidth="1"/>
+    <col min="20" max="20" width="12.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="39.6" customHeight="1">
+    <row r="1" spans="1:22" ht="14.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4507,8 +4515,8 @@
       <c r="K2" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L2" s="18" t="s">
-        <v>13</v>
+      <c r="L2" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M2" s="3">
         <v>12</v>
@@ -4571,8 +4579,8 @@
       <c r="K3" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L3" s="18" t="s">
-        <v>13</v>
+      <c r="L3" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M3" s="3">
         <v>12</v>
@@ -4639,8 +4647,8 @@
       <c r="K4" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L4" s="18" t="s">
-        <v>13</v>
+      <c r="L4" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M4" s="3">
         <v>12</v>
@@ -4707,8 +4715,8 @@
       <c r="K5" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L5" s="18" t="s">
-        <v>13</v>
+      <c r="L5" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M5" s="3">
         <v>12</v>
@@ -4775,8 +4783,8 @@
       <c r="K6" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L6" s="18" t="s">
-        <v>13</v>
+      <c r="L6" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M6" s="3">
         <v>12</v>
@@ -4839,8 +4847,8 @@
       <c r="K7" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L7" s="18" t="s">
-        <v>13</v>
+      <c r="L7" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M7" s="3">
         <v>12</v>
@@ -4907,8 +4915,8 @@
       <c r="K8" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L8" s="18" t="s">
-        <v>13</v>
+      <c r="L8" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M8" s="3">
         <v>12</v>
@@ -4975,8 +4983,8 @@
       <c r="K9" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L9" s="18" t="s">
-        <v>13</v>
+      <c r="L9" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M9" s="3">
         <v>12</v>
@@ -5043,8 +5051,8 @@
       <c r="K10" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L10" s="18" t="s">
-        <v>13</v>
+      <c r="L10" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M10" s="3">
         <v>24</v>
@@ -5107,8 +5115,8 @@
       <c r="K11" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L11" s="18" t="s">
-        <v>13</v>
+      <c r="L11" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M11" s="3">
         <v>24</v>
@@ -5175,8 +5183,8 @@
       <c r="K12" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L12" s="18" t="s">
-        <v>13</v>
+      <c r="L12" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M12" s="3">
         <v>24</v>
@@ -5243,8 +5251,8 @@
       <c r="K13" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L13" s="18" t="s">
-        <v>13</v>
+      <c r="L13" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M13" s="3">
         <v>24</v>
@@ -5311,8 +5319,8 @@
       <c r="K14" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L14" s="18" t="s">
-        <v>13</v>
+      <c r="L14" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M14" s="3">
         <v>6</v>
@@ -5375,8 +5383,8 @@
       <c r="K15" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L15" s="18" t="s">
-        <v>13</v>
+      <c r="L15" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M15" s="3">
         <v>6</v>
@@ -5443,8 +5451,8 @@
       <c r="K16" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L16" s="18" t="s">
-        <v>13</v>
+      <c r="L16" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M16" s="3">
         <v>6</v>
@@ -5511,8 +5519,8 @@
       <c r="K17" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L17" s="18" t="s">
-        <v>13</v>
+      <c r="L17" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M17" s="3">
         <v>6</v>
@@ -5579,8 +5587,8 @@
       <c r="K18" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L18" s="18" t="s">
-        <v>13</v>
+      <c r="L18" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M18" s="3">
         <v>18</v>
@@ -5643,8 +5651,8 @@
       <c r="K19" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L19" s="18" t="s">
-        <v>13</v>
+      <c r="L19" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M19" s="3">
         <v>18</v>
@@ -5711,8 +5719,8 @@
       <c r="K20" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L20" s="18" t="s">
-        <v>13</v>
+      <c r="L20" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M20" s="3">
         <v>18</v>
@@ -5779,8 +5787,8 @@
       <c r="K21" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L21" s="18" t="s">
-        <v>13</v>
+      <c r="L21" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M21" s="3">
         <v>18</v>
@@ -5847,8 +5855,8 @@
       <c r="K22" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L22" s="18" t="s">
-        <v>13</v>
+      <c r="L22" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M22" s="3">
         <v>12</v>
@@ -5911,8 +5919,8 @@
       <c r="K23" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L23" s="18" t="s">
-        <v>13</v>
+      <c r="L23" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M23" s="3">
         <v>12</v>
@@ -5979,8 +5987,8 @@
       <c r="K24" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L24" s="18" t="s">
-        <v>13</v>
+      <c r="L24" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M24" s="3">
         <v>12</v>
@@ -6047,8 +6055,8 @@
       <c r="K25" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L25" s="18" t="s">
-        <v>13</v>
+      <c r="L25" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M25" s="3">
         <v>12</v>
@@ -6115,8 +6123,8 @@
       <c r="K26" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L26" s="18" t="s">
-        <v>13</v>
+      <c r="L26" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M26" s="3">
         <v>12</v>
@@ -6179,8 +6187,8 @@
       <c r="K27" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L27" s="18" t="s">
-        <v>13</v>
+      <c r="L27" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M27" s="3">
         <v>12</v>
@@ -6247,8 +6255,8 @@
       <c r="K28" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L28" s="18" t="s">
-        <v>13</v>
+      <c r="L28" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M28" s="3">
         <v>12</v>
@@ -6315,8 +6323,8 @@
       <c r="K29" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L29" s="18" t="s">
-        <v>13</v>
+      <c r="L29" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M29" s="3">
         <v>12</v>
@@ -6383,8 +6391,8 @@
       <c r="K30" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L30" s="18" t="s">
-        <v>13</v>
+      <c r="L30" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M30" s="3">
         <v>24</v>
@@ -6447,8 +6455,8 @@
       <c r="K31" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L31" s="18" t="s">
-        <v>13</v>
+      <c r="L31" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M31" s="3">
         <v>24</v>
@@ -6515,8 +6523,8 @@
       <c r="K32" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L32" s="18" t="s">
-        <v>13</v>
+      <c r="L32" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M32" s="3">
         <v>24</v>
@@ -6583,8 +6591,8 @@
       <c r="K33" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L33" s="18" t="s">
-        <v>13</v>
+      <c r="L33" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M33" s="3">
         <v>24</v>
@@ -6651,8 +6659,8 @@
       <c r="K34" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L34" s="18" t="s">
-        <v>13</v>
+      <c r="L34" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M34" s="3">
         <v>6</v>
@@ -6715,8 +6723,8 @@
       <c r="K35" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L35" s="18" t="s">
-        <v>13</v>
+      <c r="L35" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M35" s="3">
         <v>6</v>
@@ -6783,8 +6791,8 @@
       <c r="K36" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L36" s="18" t="s">
-        <v>13</v>
+      <c r="L36" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M36" s="3">
         <v>6</v>
@@ -6851,8 +6859,8 @@
       <c r="K37" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L37" s="18" t="s">
-        <v>13</v>
+      <c r="L37" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M37" s="3">
         <v>6</v>
@@ -6919,8 +6927,8 @@
       <c r="K38" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L38" s="18" t="s">
-        <v>13</v>
+      <c r="L38" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M38" s="3">
         <v>18</v>
@@ -6983,8 +6991,8 @@
       <c r="K39" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L39" s="18" t="s">
-        <v>13</v>
+      <c r="L39" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M39" s="3">
         <v>18</v>
@@ -7051,8 +7059,8 @@
       <c r="K40" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L40" s="18" t="s">
-        <v>13</v>
+      <c r="L40" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M40" s="3">
         <v>18</v>
@@ -7119,8 +7127,8 @@
       <c r="K41" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L41" s="18" t="s">
-        <v>13</v>
+      <c r="L41" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M41" s="3">
         <v>18</v>
@@ -7187,8 +7195,8 @@
       <c r="K42" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L42" s="18" t="s">
-        <v>13</v>
+      <c r="L42" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M42" s="3">
         <v>12</v>
@@ -7251,8 +7259,8 @@
       <c r="K43" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L43" s="18" t="s">
-        <v>13</v>
+      <c r="L43" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M43" s="3">
         <v>12</v>
@@ -7319,8 +7327,8 @@
       <c r="K44" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L44" s="18" t="s">
-        <v>13</v>
+      <c r="L44" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M44" s="3">
         <v>12</v>
@@ -7387,8 +7395,8 @@
       <c r="K45" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L45" s="18" t="s">
-        <v>13</v>
+      <c r="L45" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M45" s="3">
         <v>12</v>
@@ -7455,8 +7463,8 @@
       <c r="K46" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L46" s="18" t="s">
-        <v>13</v>
+      <c r="L46" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M46" s="3">
         <v>12</v>
@@ -7519,8 +7527,8 @@
       <c r="K47" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L47" s="18" t="s">
-        <v>13</v>
+      <c r="L47" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M47" s="3">
         <v>12</v>
@@ -7587,8 +7595,8 @@
       <c r="K48" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L48" s="18" t="s">
-        <v>13</v>
+      <c r="L48" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M48" s="3">
         <v>12</v>
@@ -7655,8 +7663,8 @@
       <c r="K49" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L49" s="18" t="s">
-        <v>13</v>
+      <c r="L49" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M49" s="3">
         <v>12</v>
@@ -7723,8 +7731,8 @@
       <c r="K50" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L50" s="18" t="s">
-        <v>13</v>
+      <c r="L50" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M50" s="3">
         <v>24</v>
@@ -7787,8 +7795,8 @@
       <c r="K51" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L51" s="18" t="s">
-        <v>13</v>
+      <c r="L51" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M51" s="3">
         <v>24</v>
@@ -7855,8 +7863,8 @@
       <c r="K52" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L52" s="18" t="s">
-        <v>13</v>
+      <c r="L52" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M52" s="3">
         <v>24</v>
@@ -7923,8 +7931,8 @@
       <c r="K53" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L53" s="18" t="s">
-        <v>13</v>
+      <c r="L53" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M53" s="3">
         <v>24</v>
@@ -7991,8 +7999,8 @@
       <c r="K54" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L54" s="18" t="s">
-        <v>13</v>
+      <c r="L54" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M54" s="3">
         <v>6</v>
@@ -8055,8 +8063,8 @@
       <c r="K55" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L55" s="18" t="s">
-        <v>13</v>
+      <c r="L55" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M55" s="3">
         <v>6</v>
@@ -8123,8 +8131,8 @@
       <c r="K56" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L56" s="18" t="s">
-        <v>13</v>
+      <c r="L56" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M56" s="3">
         <v>6</v>
@@ -8191,8 +8199,8 @@
       <c r="K57" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L57" s="18" t="s">
-        <v>13</v>
+      <c r="L57" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M57" s="3">
         <v>6</v>
@@ -8259,8 +8267,8 @@
       <c r="K58" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L58" s="18" t="s">
-        <v>13</v>
+      <c r="L58" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M58" s="3">
         <v>18</v>
@@ -8323,8 +8331,8 @@
       <c r="K59" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L59" s="18" t="s">
-        <v>13</v>
+      <c r="L59" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M59" s="3">
         <v>18</v>
@@ -8391,8 +8399,8 @@
       <c r="K60" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L60" s="18" t="s">
-        <v>13</v>
+      <c r="L60" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M60" s="3">
         <v>18</v>
@@ -8459,8 +8467,8 @@
       <c r="K61" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L61" s="18" t="s">
-        <v>13</v>
+      <c r="L61" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M61" s="3">
         <v>18</v>
@@ -8527,8 +8535,8 @@
       <c r="K62" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L62" s="18" t="s">
-        <v>13</v>
+      <c r="L62" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M62" s="3">
         <v>12</v>
@@ -8591,8 +8599,8 @@
       <c r="K63" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L63" s="18" t="s">
-        <v>13</v>
+      <c r="L63" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M63" s="3">
         <v>12</v>
@@ -8659,8 +8667,8 @@
       <c r="K64" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L64" s="18" t="s">
-        <v>13</v>
+      <c r="L64" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M64" s="3">
         <v>12</v>
@@ -8727,8 +8735,8 @@
       <c r="K65" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L65" s="18" t="s">
-        <v>13</v>
+      <c r="L65" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M65" s="3">
         <v>12</v>
@@ -8795,8 +8803,8 @@
       <c r="K66" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L66" s="18" t="s">
-        <v>13</v>
+      <c r="L66" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M66" s="3">
         <v>12</v>
@@ -8859,8 +8867,8 @@
       <c r="K67" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L67" s="18" t="s">
-        <v>13</v>
+      <c r="L67" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M67" s="3">
         <v>12</v>
@@ -8927,8 +8935,8 @@
       <c r="K68" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L68" s="18" t="s">
-        <v>13</v>
+      <c r="L68" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M68" s="3">
         <v>12</v>
@@ -8995,8 +9003,8 @@
       <c r="K69" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L69" s="18" t="s">
-        <v>13</v>
+      <c r="L69" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M69" s="3">
         <v>12</v>
@@ -9063,8 +9071,8 @@
       <c r="K70" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L70" s="18" t="s">
-        <v>13</v>
+      <c r="L70" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M70" s="3">
         <v>24</v>
@@ -9127,8 +9135,8 @@
       <c r="K71" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L71" s="18" t="s">
-        <v>13</v>
+      <c r="L71" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M71" s="3">
         <v>24</v>
@@ -9195,8 +9203,8 @@
       <c r="K72" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L72" s="18" t="s">
-        <v>13</v>
+      <c r="L72" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M72" s="3">
         <v>24</v>
@@ -9263,8 +9271,8 @@
       <c r="K73" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L73" s="18" t="s">
-        <v>13</v>
+      <c r="L73" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M73" s="3">
         <v>24</v>
@@ -9331,8 +9339,8 @@
       <c r="K74" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L74" s="18" t="s">
-        <v>13</v>
+      <c r="L74" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M74" s="3">
         <v>6</v>
@@ -9395,8 +9403,8 @@
       <c r="K75" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L75" s="18" t="s">
-        <v>13</v>
+      <c r="L75" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M75" s="3">
         <v>6</v>
@@ -9463,8 +9471,8 @@
       <c r="K76" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L76" s="18" t="s">
-        <v>13</v>
+      <c r="L76" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M76" s="3">
         <v>6</v>
@@ -9531,8 +9539,8 @@
       <c r="K77" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L77" s="18" t="s">
-        <v>13</v>
+      <c r="L77" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M77" s="3">
         <v>6</v>
@@ -9599,8 +9607,8 @@
       <c r="K78" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L78" s="18" t="s">
-        <v>13</v>
+      <c r="L78" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M78" s="3">
         <v>18</v>
@@ -9663,8 +9671,8 @@
       <c r="K79" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L79" s="18" t="s">
-        <v>13</v>
+      <c r="L79" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M79" s="3">
         <v>18</v>
@@ -9731,8 +9739,8 @@
       <c r="K80" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L80" s="18" t="s">
-        <v>13</v>
+      <c r="L80" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M80" s="3">
         <v>18</v>
@@ -9799,8 +9807,8 @@
       <c r="K81" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L81" s="18" t="s">
-        <v>13</v>
+      <c r="L81" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M81" s="3">
         <v>18</v>
@@ -9867,8 +9875,8 @@
       <c r="K82" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L82" s="18" t="s">
-        <v>13</v>
+      <c r="L82" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M82" s="3">
         <v>12</v>
@@ -9931,8 +9939,8 @@
       <c r="K83" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L83" s="18" t="s">
-        <v>13</v>
+      <c r="L83" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M83" s="3">
         <v>12</v>
@@ -9999,8 +10007,8 @@
       <c r="K84" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L84" s="18" t="s">
-        <v>13</v>
+      <c r="L84" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M84" s="3">
         <v>12</v>
@@ -10067,8 +10075,8 @@
       <c r="K85" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L85" s="18" t="s">
-        <v>13</v>
+      <c r="L85" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M85" s="3">
         <v>12</v>
@@ -10135,8 +10143,8 @@
       <c r="K86" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L86" s="18" t="s">
-        <v>13</v>
+      <c r="L86" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M86" s="3">
         <v>12</v>
@@ -10199,8 +10207,8 @@
       <c r="K87" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L87" s="18" t="s">
-        <v>13</v>
+      <c r="L87" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M87" s="3">
         <v>12</v>
@@ -10267,8 +10275,8 @@
       <c r="K88" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L88" s="18" t="s">
-        <v>13</v>
+      <c r="L88" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M88" s="3">
         <v>12</v>
@@ -10335,8 +10343,8 @@
       <c r="K89" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L89" s="18" t="s">
-        <v>13</v>
+      <c r="L89" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M89" s="3">
         <v>12</v>
@@ -10403,8 +10411,8 @@
       <c r="K90" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L90" s="18" t="s">
-        <v>13</v>
+      <c r="L90" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M90" s="3">
         <v>24</v>
@@ -10467,8 +10475,8 @@
       <c r="K91" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L91" s="18" t="s">
-        <v>13</v>
+      <c r="L91" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M91" s="3">
         <v>24</v>
@@ -10535,8 +10543,8 @@
       <c r="K92" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L92" s="18" t="s">
-        <v>13</v>
+      <c r="L92" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M92" s="3">
         <v>24</v>
@@ -10603,8 +10611,8 @@
       <c r="K93" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L93" s="18" t="s">
-        <v>13</v>
+      <c r="L93" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M93" s="3">
         <v>24</v>
@@ -10671,8 +10679,8 @@
       <c r="K94" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L94" s="18" t="s">
-        <v>13</v>
+      <c r="L94" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M94" s="3">
         <v>6</v>
@@ -10735,8 +10743,8 @@
       <c r="K95" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L95" s="18" t="s">
-        <v>13</v>
+      <c r="L95" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M95" s="3">
         <v>6</v>
@@ -10803,8 +10811,8 @@
       <c r="K96" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L96" s="18" t="s">
-        <v>13</v>
+      <c r="L96" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M96" s="3">
         <v>6</v>
@@ -10871,8 +10879,8 @@
       <c r="K97" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L97" s="18" t="s">
-        <v>13</v>
+      <c r="L97" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M97" s="3">
         <v>6</v>
@@ -10939,8 +10947,8 @@
       <c r="K98" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L98" s="18" t="s">
-        <v>13</v>
+      <c r="L98" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M98" s="3">
         <v>18</v>
@@ -11003,8 +11011,8 @@
       <c r="K99" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L99" s="18" t="s">
-        <v>13</v>
+      <c r="L99" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M99" s="3">
         <v>18</v>
@@ -11071,8 +11079,8 @@
       <c r="K100" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L100" s="18" t="s">
-        <v>13</v>
+      <c r="L100" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M100" s="3">
         <v>18</v>
@@ -11139,8 +11147,8 @@
       <c r="K101" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L101" s="18" t="s">
-        <v>13</v>
+      <c r="L101" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M101" s="3">
         <v>18</v>
@@ -11207,8 +11215,8 @@
       <c r="K102" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L102" s="18" t="s">
-        <v>13</v>
+      <c r="L102" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M102" s="3">
         <v>12</v>
@@ -11271,8 +11279,8 @@
       <c r="K103" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L103" s="18" t="s">
-        <v>13</v>
+      <c r="L103" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M103" s="3">
         <v>12</v>
@@ -11339,8 +11347,8 @@
       <c r="K104" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L104" s="18" t="s">
-        <v>13</v>
+      <c r="L104" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M104" s="3">
         <v>12</v>
@@ -11407,8 +11415,8 @@
       <c r="K105" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L105" s="18" t="s">
-        <v>13</v>
+      <c r="L105" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M105" s="3">
         <v>12</v>
@@ -11475,8 +11483,8 @@
       <c r="K106" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L106" s="18" t="s">
-        <v>13</v>
+      <c r="L106" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M106" s="3">
         <v>12</v>
@@ -11539,8 +11547,8 @@
       <c r="K107" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L107" s="18" t="s">
-        <v>13</v>
+      <c r="L107" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M107" s="3">
         <v>12</v>
@@ -11607,8 +11615,8 @@
       <c r="K108" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L108" s="18" t="s">
-        <v>13</v>
+      <c r="L108" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M108" s="3">
         <v>12</v>
@@ -11675,8 +11683,8 @@
       <c r="K109" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L109" s="18" t="s">
-        <v>13</v>
+      <c r="L109" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M109" s="3">
         <v>12</v>
@@ -11743,8 +11751,8 @@
       <c r="K110" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L110" s="18" t="s">
-        <v>13</v>
+      <c r="L110" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M110" s="3">
         <v>18</v>
@@ -11807,8 +11815,8 @@
       <c r="K111" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L111" s="18" t="s">
-        <v>13</v>
+      <c r="L111" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M111" s="3">
         <v>18</v>
@@ -11875,8 +11883,8 @@
       <c r="K112" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L112" s="18" t="s">
-        <v>13</v>
+      <c r="L112" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M112" s="3">
         <v>18</v>
@@ -11943,8 +11951,8 @@
       <c r="K113" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L113" s="18" t="s">
-        <v>13</v>
+      <c r="L113" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M113" s="3">
         <v>18</v>
@@ -12011,8 +12019,8 @@
       <c r="K114" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L114" s="18" t="s">
-        <v>13</v>
+      <c r="L114" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M114" s="3">
         <v>12</v>
@@ -12075,8 +12083,8 @@
       <c r="K115" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L115" s="18" t="s">
-        <v>13</v>
+      <c r="L115" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M115" s="3">
         <v>12</v>
@@ -12143,8 +12151,8 @@
       <c r="K116" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L116" s="18" t="s">
-        <v>13</v>
+      <c r="L116" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M116" s="3">
         <v>12</v>
@@ -12211,8 +12219,8 @@
       <c r="K117" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L117" s="18" t="s">
-        <v>13</v>
+      <c r="L117" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M117" s="3">
         <v>12</v>
@@ -12279,8 +12287,8 @@
       <c r="K118" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L118" s="18" t="s">
-        <v>13</v>
+      <c r="L118" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M118" s="3">
         <v>12</v>
@@ -12343,8 +12351,8 @@
       <c r="K119" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L119" s="18" t="s">
-        <v>13</v>
+      <c r="L119" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M119" s="3">
         <v>12</v>
@@ -12411,8 +12419,8 @@
       <c r="K120" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L120" s="18" t="s">
-        <v>13</v>
+      <c r="L120" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M120" s="3">
         <v>12</v>
@@ -12479,8 +12487,8 @@
       <c r="K121" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L121" s="18" t="s">
-        <v>13</v>
+      <c r="L121" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M121" s="3">
         <v>12</v>
@@ -12547,8 +12555,8 @@
       <c r="K122" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L122" s="18" t="s">
-        <v>13</v>
+      <c r="L122" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M122" s="3">
         <v>18</v>
@@ -12611,8 +12619,8 @@
       <c r="K123" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L123" s="18" t="s">
-        <v>13</v>
+      <c r="L123" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M123" s="3">
         <v>18</v>
@@ -12679,8 +12687,8 @@
       <c r="K124" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L124" s="18" t="s">
-        <v>13</v>
+      <c r="L124" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M124" s="3">
         <v>18</v>
@@ -12747,8 +12755,8 @@
       <c r="K125" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L125" s="18" t="s">
-        <v>13</v>
+      <c r="L125" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M125" s="3">
         <v>18</v>
@@ -12815,8 +12823,8 @@
       <c r="K126" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L126" s="18" t="s">
-        <v>13</v>
+      <c r="L126" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M126" s="3">
         <v>12</v>
@@ -12879,8 +12887,8 @@
       <c r="K127" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L127" s="18" t="s">
-        <v>13</v>
+      <c r="L127" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M127" s="3">
         <v>12</v>
@@ -12947,8 +12955,8 @@
       <c r="K128" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L128" s="18" t="s">
-        <v>13</v>
+      <c r="L128" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M128" s="3">
         <v>12</v>
@@ -13015,8 +13023,8 @@
       <c r="K129" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L129" s="18" t="s">
-        <v>13</v>
+      <c r="L129" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M129" s="3">
         <v>12</v>
@@ -13083,8 +13091,8 @@
       <c r="K130" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L130" s="18" t="s">
-        <v>13</v>
+      <c r="L130" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M130" s="3">
         <v>12</v>
@@ -13147,8 +13155,8 @@
       <c r="K131" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L131" s="18" t="s">
-        <v>13</v>
+      <c r="L131" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M131" s="3">
         <v>12</v>
@@ -13215,8 +13223,8 @@
       <c r="K132" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L132" s="18" t="s">
-        <v>13</v>
+      <c r="L132" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M132" s="3">
         <v>12</v>
@@ -13283,8 +13291,8 @@
       <c r="K133" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L133" s="18" t="s">
-        <v>13</v>
+      <c r="L133" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M133" s="3">
         <v>12</v>
@@ -13351,8 +13359,8 @@
       <c r="K134" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L134" s="18" t="s">
-        <v>13</v>
+      <c r="L134" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M134" s="3">
         <v>18</v>
@@ -13415,8 +13423,8 @@
       <c r="K135" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L135" s="18" t="s">
-        <v>13</v>
+      <c r="L135" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M135" s="3">
         <v>18</v>
@@ -13483,8 +13491,8 @@
       <c r="K136" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L136" s="18" t="s">
-        <v>13</v>
+      <c r="L136" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M136" s="3">
         <v>18</v>
@@ -13551,8 +13559,8 @@
       <c r="K137" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L137" s="18" t="s">
-        <v>13</v>
+      <c r="L137" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M137" s="3">
         <v>18</v>
@@ -13619,8 +13627,8 @@
       <c r="K138" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L138" s="18" t="s">
-        <v>13</v>
+      <c r="L138" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M138" s="3">
         <v>12</v>
@@ -13683,8 +13691,8 @@
       <c r="K139" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L139" s="18" t="s">
-        <v>13</v>
+      <c r="L139" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M139" s="3">
         <v>12</v>
@@ -13751,8 +13759,8 @@
       <c r="K140" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L140" s="18" t="s">
-        <v>13</v>
+      <c r="L140" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M140" s="3">
         <v>12</v>
@@ -13819,8 +13827,8 @@
       <c r="K141" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L141" s="18" t="s">
-        <v>13</v>
+      <c r="L141" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M141" s="3">
         <v>12</v>
@@ -13887,8 +13895,8 @@
       <c r="K142" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L142" s="18" t="s">
-        <v>13</v>
+      <c r="L142" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M142" s="3">
         <v>12</v>
@@ -13951,8 +13959,8 @@
       <c r="K143" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L143" s="18" t="s">
-        <v>13</v>
+      <c r="L143" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M143" s="3">
         <v>12</v>
@@ -14019,8 +14027,8 @@
       <c r="K144" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L144" s="18" t="s">
-        <v>13</v>
+      <c r="L144" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M144" s="3">
         <v>12</v>
@@ -14087,8 +14095,8 @@
       <c r="K145" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L145" s="18" t="s">
-        <v>13</v>
+      <c r="L145" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M145" s="3">
         <v>12</v>
@@ -14155,8 +14163,8 @@
       <c r="K146" s="18" t="s">
         <v>809</v>
       </c>
-      <c r="L146" s="18" t="s">
-        <v>13</v>
+      <c r="L146" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M146" s="3">
         <v>18</v>
@@ -14219,8 +14227,8 @@
       <c r="K147" s="18" t="s">
         <v>809</v>
       </c>
-      <c r="L147" s="18" t="s">
-        <v>13</v>
+      <c r="L147" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M147" s="3">
         <v>18</v>
@@ -14287,8 +14295,8 @@
       <c r="K148" s="18" t="s">
         <v>809</v>
       </c>
-      <c r="L148" s="18" t="s">
-        <v>13</v>
+      <c r="L148" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M148" s="3">
         <v>18</v>
@@ -14355,8 +14363,8 @@
       <c r="K149" s="18" t="s">
         <v>809</v>
       </c>
-      <c r="L149" s="18" t="s">
-        <v>13</v>
+      <c r="L149" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M149" s="3">
         <v>18</v>
@@ -14423,8 +14431,8 @@
       <c r="K150" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L150" s="18" t="s">
-        <v>13</v>
+      <c r="L150" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M150" s="3">
         <v>12</v>
@@ -14487,8 +14495,8 @@
       <c r="K151" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L151" s="18" t="s">
-        <v>13</v>
+      <c r="L151" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M151" s="3">
         <v>12</v>
@@ -14555,8 +14563,8 @@
       <c r="K152" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L152" s="18" t="s">
-        <v>13</v>
+      <c r="L152" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M152" s="3">
         <v>12</v>
@@ -14623,8 +14631,8 @@
       <c r="K153" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L153" s="18" t="s">
-        <v>13</v>
+      <c r="L153" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M153" s="3">
         <v>12</v>
@@ -14691,8 +14699,8 @@
       <c r="K154" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L154" s="18" t="s">
-        <v>13</v>
+      <c r="L154" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M154" s="3">
         <v>12</v>
@@ -14755,8 +14763,8 @@
       <c r="K155" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L155" s="18" t="s">
-        <v>13</v>
+      <c r="L155" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M155" s="3">
         <v>12</v>
@@ -14823,8 +14831,8 @@
       <c r="K156" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L156" s="18" t="s">
-        <v>13</v>
+      <c r="L156" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M156" s="3">
         <v>12</v>
@@ -14891,8 +14899,8 @@
       <c r="K157" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L157" s="18" t="s">
-        <v>13</v>
+      <c r="L157" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M157" s="3">
         <v>12</v>
@@ -14959,8 +14967,8 @@
       <c r="K158" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L158" s="18" t="s">
-        <v>13</v>
+      <c r="L158" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M158" s="3">
         <v>18</v>
@@ -15023,8 +15031,8 @@
       <c r="K159" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L159" s="18" t="s">
-        <v>13</v>
+      <c r="L159" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M159" s="3">
         <v>18</v>
@@ -15091,8 +15099,8 @@
       <c r="K160" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L160" s="18" t="s">
-        <v>13</v>
+      <c r="L160" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M160" s="3">
         <v>18</v>
@@ -15159,8 +15167,8 @@
       <c r="K161" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L161" s="18" t="s">
-        <v>13</v>
+      <c r="L161" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M161" s="3">
         <v>18</v>
@@ -15227,8 +15235,8 @@
       <c r="K162" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L162" s="18" t="s">
-        <v>13</v>
+      <c r="L162" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M162" s="3">
         <v>12</v>
@@ -15291,8 +15299,8 @@
       <c r="K163" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L163" s="18" t="s">
-        <v>13</v>
+      <c r="L163" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M163" s="3">
         <v>12</v>
@@ -15359,8 +15367,8 @@
       <c r="K164" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L164" s="18" t="s">
-        <v>13</v>
+      <c r="L164" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M164" s="3">
         <v>12</v>
@@ -15427,8 +15435,8 @@
       <c r="K165" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L165" s="18" t="s">
-        <v>13</v>
+      <c r="L165" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M165" s="3">
         <v>12</v>
@@ -15495,8 +15503,8 @@
       <c r="K166" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L166" s="18" t="s">
-        <v>13</v>
+      <c r="L166" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M166" s="3">
         <v>12</v>
@@ -15559,8 +15567,8 @@
       <c r="K167" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L167" s="18" t="s">
-        <v>13</v>
+      <c r="L167" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M167" s="3">
         <v>12</v>
@@ -15627,8 +15635,8 @@
       <c r="K168" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L168" s="18" t="s">
-        <v>13</v>
+      <c r="L168" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M168" s="3">
         <v>12</v>
@@ -15695,8 +15703,8 @@
       <c r="K169" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L169" s="18" t="s">
-        <v>13</v>
+      <c r="L169" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M169" s="3">
         <v>12</v>
@@ -15763,8 +15771,8 @@
       <c r="K170" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L170" s="18" t="s">
-        <v>13</v>
+      <c r="L170" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M170" s="3">
         <v>18</v>
@@ -15827,8 +15835,8 @@
       <c r="K171" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L171" s="18" t="s">
-        <v>13</v>
+      <c r="L171" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M171" s="3">
         <v>18</v>
@@ -15895,8 +15903,8 @@
       <c r="K172" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L172" s="18" t="s">
-        <v>13</v>
+      <c r="L172" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M172" s="3">
         <v>18</v>
@@ -15963,8 +15971,8 @@
       <c r="K173" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L173" s="18" t="s">
-        <v>13</v>
+      <c r="L173" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M173" s="3">
         <v>18</v>
@@ -16031,8 +16039,8 @@
       <c r="K174" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L174" s="18" t="s">
-        <v>13</v>
+      <c r="L174" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M174" s="3">
         <v>12</v>
@@ -16095,8 +16103,8 @@
       <c r="K175" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L175" s="18" t="s">
-        <v>13</v>
+      <c r="L175" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M175" s="3">
         <v>12</v>
@@ -16163,8 +16171,8 @@
       <c r="K176" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L176" s="18" t="s">
-        <v>13</v>
+      <c r="L176" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M176" s="3">
         <v>12</v>
@@ -16231,8 +16239,8 @@
       <c r="K177" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L177" s="18" t="s">
-        <v>13</v>
+      <c r="L177" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M177" s="3">
         <v>12</v>
@@ -16299,8 +16307,8 @@
       <c r="K178" s="18" t="s">
         <v>818</v>
       </c>
-      <c r="L178" s="18" t="s">
-        <v>13</v>
+      <c r="L178" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M178" s="3">
         <v>12</v>
@@ -16363,8 +16371,8 @@
       <c r="K179" s="18" t="s">
         <v>818</v>
       </c>
-      <c r="L179" s="18" t="s">
-        <v>13</v>
+      <c r="L179" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M179" s="3">
         <v>12</v>
@@ -16431,8 +16439,8 @@
       <c r="K180" s="18" t="s">
         <v>818</v>
       </c>
-      <c r="L180" s="18" t="s">
-        <v>13</v>
+      <c r="L180" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M180" s="3">
         <v>12</v>
@@ -16499,8 +16507,8 @@
       <c r="K181" s="18" t="s">
         <v>818</v>
       </c>
-      <c r="L181" s="18" t="s">
-        <v>13</v>
+      <c r="L181" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M181" s="3">
         <v>12</v>
@@ -16567,8 +16575,8 @@
       <c r="K182" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L182" s="18" t="s">
-        <v>13</v>
+      <c r="L182" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M182" s="3">
         <v>18</v>
@@ -16631,8 +16639,8 @@
       <c r="K183" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L183" s="18" t="s">
-        <v>13</v>
+      <c r="L183" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M183" s="3">
         <v>18</v>
@@ -16699,8 +16707,8 @@
       <c r="K184" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L184" s="18" t="s">
-        <v>13</v>
+      <c r="L184" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M184" s="3">
         <v>18</v>
@@ -16767,8 +16775,8 @@
       <c r="K185" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L185" s="18" t="s">
-        <v>13</v>
+      <c r="L185" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M185" s="3">
         <v>18</v>
@@ -16835,8 +16843,8 @@
       <c r="K186" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L186" s="18" t="s">
-        <v>13</v>
+      <c r="L186" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M186" s="3">
         <v>12</v>
@@ -16899,8 +16907,8 @@
       <c r="K187" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L187" s="18" t="s">
-        <v>13</v>
+      <c r="L187" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M187" s="3">
         <v>12</v>
@@ -16967,8 +16975,8 @@
       <c r="K188" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L188" s="18" t="s">
-        <v>13</v>
+      <c r="L188" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M188" s="3">
         <v>12</v>
@@ -17035,8 +17043,8 @@
       <c r="K189" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L189" s="18" t="s">
-        <v>13</v>
+      <c r="L189" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M189" s="3">
         <v>12</v>
@@ -17103,8 +17111,8 @@
       <c r="K190" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L190" s="18" t="s">
-        <v>13</v>
+      <c r="L190" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M190" s="3">
         <v>12</v>
@@ -17167,8 +17175,8 @@
       <c r="K191" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L191" s="18" t="s">
-        <v>13</v>
+      <c r="L191" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M191" s="3">
         <v>12</v>
@@ -17235,8 +17243,8 @@
       <c r="K192" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L192" s="18" t="s">
-        <v>13</v>
+      <c r="L192" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M192" s="3">
         <v>12</v>
@@ -17303,8 +17311,8 @@
       <c r="K193" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L193" s="18" t="s">
-        <v>13</v>
+      <c r="L193" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M193" s="3">
         <v>12</v>
@@ -17371,8 +17379,8 @@
       <c r="K194" s="18" t="s">
         <v>827</v>
       </c>
-      <c r="L194" s="18" t="s">
-        <v>13</v>
+      <c r="L194" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M194" s="3">
         <v>18</v>
@@ -17435,8 +17443,8 @@
       <c r="K195" s="18" t="s">
         <v>827</v>
       </c>
-      <c r="L195" s="18" t="s">
-        <v>13</v>
+      <c r="L195" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M195" s="3">
         <v>18</v>
@@ -17503,8 +17511,8 @@
       <c r="K196" s="18" t="s">
         <v>827</v>
       </c>
-      <c r="L196" s="18" t="s">
-        <v>13</v>
+      <c r="L196" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M196" s="3">
         <v>18</v>
@@ -17571,8 +17579,8 @@
       <c r="K197" s="18" t="s">
         <v>827</v>
       </c>
-      <c r="L197" s="18" t="s">
-        <v>13</v>
+      <c r="L197" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M197" s="3">
         <v>18</v>
@@ -17639,8 +17647,8 @@
       <c r="K198" s="18" t="s">
         <v>827</v>
       </c>
-      <c r="L198" s="18" t="s">
-        <v>13</v>
+      <c r="L198" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M198" s="3">
         <v>12</v>
@@ -17703,8 +17711,8 @@
       <c r="K199" s="18" t="s">
         <v>827</v>
       </c>
-      <c r="L199" s="18" t="s">
-        <v>13</v>
+      <c r="L199" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M199" s="3">
         <v>12</v>
@@ -17771,8 +17779,8 @@
       <c r="K200" s="18" t="s">
         <v>827</v>
       </c>
-      <c r="L200" s="18" t="s">
-        <v>13</v>
+      <c r="L200" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M200" s="3">
         <v>12</v>
@@ -17839,8 +17847,8 @@
       <c r="K201" s="18" t="s">
         <v>827</v>
       </c>
-      <c r="L201" s="18" t="s">
-        <v>13</v>
+      <c r="L201" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M201" s="3">
         <v>12</v>
@@ -17907,8 +17915,8 @@
       <c r="K202" s="18" t="s">
         <v>837</v>
       </c>
-      <c r="L202" s="18" t="s">
-        <v>13</v>
+      <c r="L202" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M202" s="3">
         <v>12</v>
@@ -17971,8 +17979,8 @@
       <c r="K203" s="18" t="s">
         <v>837</v>
       </c>
-      <c r="L203" s="18" t="s">
-        <v>13</v>
+      <c r="L203" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M203" s="3">
         <v>12</v>
@@ -18039,8 +18047,8 @@
       <c r="K204" s="18" t="s">
         <v>837</v>
       </c>
-      <c r="L204" s="18" t="s">
-        <v>13</v>
+      <c r="L204" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M204" s="3">
         <v>12</v>
@@ -18107,8 +18115,8 @@
       <c r="K205" s="18" t="s">
         <v>837</v>
       </c>
-      <c r="L205" s="18" t="s">
-        <v>13</v>
+      <c r="L205" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M205" s="3">
         <v>12</v>
@@ -18175,8 +18183,8 @@
       <c r="K206" s="18" t="s">
         <v>818</v>
       </c>
-      <c r="L206" s="18" t="s">
-        <v>13</v>
+      <c r="L206" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M206" s="3">
         <v>24</v>
@@ -18239,8 +18247,8 @@
       <c r="K207" s="18" t="s">
         <v>818</v>
       </c>
-      <c r="L207" s="18" t="s">
-        <v>13</v>
+      <c r="L207" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M207" s="3">
         <v>24</v>
@@ -18307,8 +18315,8 @@
       <c r="K208" s="18" t="s">
         <v>818</v>
       </c>
-      <c r="L208" s="18" t="s">
-        <v>13</v>
+      <c r="L208" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M208" s="3">
         <v>24</v>
@@ -18375,8 +18383,8 @@
       <c r="K209" s="18" t="s">
         <v>818</v>
       </c>
-      <c r="L209" s="18" t="s">
-        <v>13</v>
+      <c r="L209" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M209" s="3">
         <v>24</v>
@@ -18443,8 +18451,8 @@
       <c r="K210" s="18" t="s">
         <v>809</v>
       </c>
-      <c r="L210" s="18" t="s">
-        <v>13</v>
+      <c r="L210" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M210" s="3">
         <v>6</v>
@@ -18507,8 +18515,8 @@
       <c r="K211" s="18" t="s">
         <v>809</v>
       </c>
-      <c r="L211" s="18" t="s">
-        <v>13</v>
+      <c r="L211" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M211" s="3">
         <v>6</v>
@@ -18575,8 +18583,8 @@
       <c r="K212" s="18" t="s">
         <v>809</v>
       </c>
-      <c r="L212" s="18" t="s">
-        <v>13</v>
+      <c r="L212" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M212" s="3">
         <v>6</v>
@@ -18643,8 +18651,8 @@
       <c r="K213" s="18" t="s">
         <v>809</v>
       </c>
-      <c r="L213" s="18" t="s">
-        <v>13</v>
+      <c r="L213" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M213" s="3">
         <v>6</v>
@@ -18711,8 +18719,8 @@
       <c r="K214" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L214" s="18" t="s">
-        <v>13</v>
+      <c r="L214" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M214" s="3">
         <v>18</v>
@@ -18775,8 +18783,8 @@
       <c r="K215" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L215" s="18" t="s">
-        <v>13</v>
+      <c r="L215" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M215" s="3">
         <v>18</v>
@@ -18843,8 +18851,8 @@
       <c r="K216" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L216" s="18" t="s">
-        <v>13</v>
+      <c r="L216" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M216" s="3">
         <v>18</v>
@@ -18911,8 +18919,8 @@
       <c r="K217" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L217" s="18" t="s">
-        <v>13</v>
+      <c r="L217" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M217" s="3">
         <v>18</v>
@@ -18979,8 +18987,8 @@
       <c r="K218" s="18" t="s">
         <v>809</v>
       </c>
-      <c r="L218" s="18" t="s">
-        <v>13</v>
+      <c r="L218" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M218" s="3">
         <v>12</v>
@@ -19043,8 +19051,8 @@
       <c r="K219" s="18" t="s">
         <v>809</v>
       </c>
-      <c r="L219" s="18" t="s">
-        <v>13</v>
+      <c r="L219" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M219" s="3">
         <v>12</v>
@@ -19111,8 +19119,8 @@
       <c r="K220" s="18" t="s">
         <v>809</v>
       </c>
-      <c r="L220" s="18" t="s">
-        <v>13</v>
+      <c r="L220" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M220" s="3">
         <v>12</v>
@@ -19179,8 +19187,8 @@
       <c r="K221" s="18" t="s">
         <v>809</v>
       </c>
-      <c r="L221" s="18" t="s">
-        <v>13</v>
+      <c r="L221" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M221" s="3">
         <v>12</v>
@@ -19247,8 +19255,8 @@
       <c r="K222" s="18" t="s">
         <v>853</v>
       </c>
-      <c r="L222" s="18" t="s">
-        <v>13</v>
+      <c r="L222" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M222" s="3">
         <v>12</v>
@@ -19311,8 +19319,8 @@
       <c r="K223" s="18" t="s">
         <v>853</v>
       </c>
-      <c r="L223" s="18" t="s">
-        <v>13</v>
+      <c r="L223" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M223" s="3">
         <v>12</v>
@@ -19379,8 +19387,8 @@
       <c r="K224" s="18" t="s">
         <v>853</v>
       </c>
-      <c r="L224" s="18" t="s">
-        <v>13</v>
+      <c r="L224" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M224" s="3">
         <v>12</v>
@@ -19447,8 +19455,8 @@
       <c r="K225" s="18" t="s">
         <v>853</v>
       </c>
-      <c r="L225" s="18" t="s">
-        <v>13</v>
+      <c r="L225" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M225" s="3">
         <v>12</v>
@@ -19515,8 +19523,8 @@
       <c r="K226" s="18" t="s">
         <v>856</v>
       </c>
-      <c r="L226" s="18" t="s">
-        <v>13</v>
+      <c r="L226" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M226" s="3">
         <v>24</v>
@@ -19579,8 +19587,8 @@
       <c r="K227" s="18" t="s">
         <v>856</v>
       </c>
-      <c r="L227" s="18" t="s">
-        <v>13</v>
+      <c r="L227" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M227" s="3">
         <v>24</v>
@@ -19647,8 +19655,8 @@
       <c r="K228" s="18" t="s">
         <v>856</v>
       </c>
-      <c r="L228" s="18" t="s">
-        <v>13</v>
+      <c r="L228" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M228" s="3">
         <v>24</v>
@@ -19715,8 +19723,8 @@
       <c r="K229" s="18" t="s">
         <v>856</v>
       </c>
-      <c r="L229" s="18" t="s">
-        <v>13</v>
+      <c r="L229" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M229" s="3">
         <v>24</v>
@@ -19749,7 +19757,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="230" spans="1:22">
+    <row r="230" spans="1:22" ht="14.4">
       <c r="A230" s="17" t="s">
         <v>375</v>
       </c>
@@ -19783,8 +19791,8 @@
       <c r="K230" s="18" t="s">
         <v>853</v>
       </c>
-      <c r="L230" s="18" t="s">
-        <v>13</v>
+      <c r="L230" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M230" s="3">
         <v>6</v>
@@ -19813,7 +19821,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="231" spans="1:22" ht="15">
+    <row r="231" spans="1:22" ht="14.4">
       <c r="A231" s="17" t="s">
         <v>375</v>
       </c>
@@ -19847,8 +19855,8 @@
       <c r="K231" s="18" t="s">
         <v>853</v>
       </c>
-      <c r="L231" s="18" t="s">
-        <v>13</v>
+      <c r="L231" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M231" s="3">
         <v>6</v>
@@ -19881,7 +19889,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="232" spans="1:22" ht="15">
+    <row r="232" spans="1:22" ht="14.4">
       <c r="A232" s="17" t="s">
         <v>375</v>
       </c>
@@ -19915,8 +19923,8 @@
       <c r="K232" s="18" t="s">
         <v>853</v>
       </c>
-      <c r="L232" s="18" t="s">
-        <v>13</v>
+      <c r="L232" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M232" s="3">
         <v>6</v>
@@ -19949,7 +19957,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="233" spans="1:22">
+    <row r="233" spans="1:22" ht="14.4">
       <c r="A233" s="17" t="s">
         <v>375</v>
       </c>
@@ -19983,8 +19991,8 @@
       <c r="K233" s="18" t="s">
         <v>853</v>
       </c>
-      <c r="L233" s="18" t="s">
-        <v>13</v>
+      <c r="L233" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M233" s="3">
         <v>6</v>
@@ -20017,7 +20025,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="234" spans="1:22">
+    <row r="234" spans="1:22" ht="14.4">
       <c r="A234" s="17" t="s">
         <v>376</v>
       </c>
@@ -20051,8 +20059,8 @@
       <c r="K234" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L234" s="18" t="s">
-        <v>13</v>
+      <c r="L234" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M234" s="3">
         <v>18</v>
@@ -20081,7 +20089,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="235" spans="1:22">
+    <row r="235" spans="1:22" ht="14.4">
       <c r="A235" s="17" t="s">
         <v>376</v>
       </c>
@@ -20115,8 +20123,8 @@
       <c r="K235" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L235" s="18" t="s">
-        <v>13</v>
+      <c r="L235" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M235" s="3">
         <v>18</v>
@@ -20149,7 +20157,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="236" spans="1:22" ht="15">
+    <row r="236" spans="1:22" ht="14.4">
       <c r="A236" s="17" t="s">
         <v>376</v>
       </c>
@@ -20183,8 +20191,8 @@
       <c r="K236" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L236" s="18" t="s">
-        <v>13</v>
+      <c r="L236" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M236" s="3">
         <v>18</v>
@@ -20217,7 +20225,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="237" spans="1:22">
+    <row r="237" spans="1:22" ht="14.4">
       <c r="A237" s="17" t="s">
         <v>376</v>
       </c>
@@ -20251,8 +20259,8 @@
       <c r="K237" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L237" s="18" t="s">
-        <v>13</v>
+      <c r="L237" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M237" s="3">
         <v>18</v>
@@ -20285,7 +20293,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="238" spans="1:22" ht="15">
+    <row r="238" spans="1:22" ht="14.4">
       <c r="A238" s="17" t="s">
         <v>379</v>
       </c>
@@ -20319,8 +20327,8 @@
       <c r="K238" s="18" t="s">
         <v>853</v>
       </c>
-      <c r="L238" s="18" t="s">
-        <v>13</v>
+      <c r="L238" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M238" s="3">
         <v>12</v>
@@ -20349,7 +20357,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="239" spans="1:22" ht="15">
+    <row r="239" spans="1:22" ht="14.4">
       <c r="A239" s="17" t="s">
         <v>379</v>
       </c>
@@ -20383,8 +20391,8 @@
       <c r="K239" s="18" t="s">
         <v>853</v>
       </c>
-      <c r="L239" s="18" t="s">
-        <v>13</v>
+      <c r="L239" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M239" s="3">
         <v>12</v>
@@ -20417,7 +20425,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="240" spans="1:22" ht="15">
+    <row r="240" spans="1:22" ht="14.4">
       <c r="A240" s="17" t="s">
         <v>379</v>
       </c>
@@ -20451,8 +20459,8 @@
       <c r="K240" s="18" t="s">
         <v>853</v>
       </c>
-      <c r="L240" s="18" t="s">
-        <v>13</v>
+      <c r="L240" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M240" s="3">
         <v>12</v>
@@ -20485,7 +20493,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="241" spans="1:22" ht="15">
+    <row r="241" spans="1:22" ht="14.4">
       <c r="A241" s="22" t="s">
         <v>379</v>
       </c>
@@ -20519,8 +20527,8 @@
       <c r="K241" s="22" t="s">
         <v>853</v>
       </c>
-      <c r="L241" s="22" t="s">
-        <v>13</v>
+      <c r="L241" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M241" s="13">
         <v>12</v>
@@ -20553,7 +20561,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="242" spans="1:22">
+    <row r="242" spans="1:22" ht="14.4">
       <c r="A242" s="17" t="s">
         <v>618</v>
       </c>
@@ -20587,8 +20595,8 @@
       <c r="K242" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L242" s="18" t="s">
-        <v>13</v>
+      <c r="L242" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M242" s="3">
         <v>18</v>
@@ -20617,7 +20625,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="243" spans="1:22" ht="15">
+    <row r="243" spans="1:22" ht="14.4">
       <c r="A243" s="17" t="s">
         <v>618</v>
       </c>
@@ -20651,8 +20659,8 @@
       <c r="K243" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L243" s="18" t="s">
-        <v>13</v>
+      <c r="L243" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M243" s="3">
         <v>18</v>
@@ -20685,7 +20693,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="244" spans="1:22" ht="15">
+    <row r="244" spans="1:22" ht="14.4">
       <c r="A244" s="17" t="s">
         <v>618</v>
       </c>
@@ -20719,8 +20727,8 @@
       <c r="K244" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L244" s="18" t="s">
-        <v>13</v>
+      <c r="L244" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M244" s="3">
         <v>18</v>
@@ -20753,7 +20761,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="245" spans="1:22">
+    <row r="245" spans="1:22" ht="14.4">
       <c r="A245" s="17" t="s">
         <v>618</v>
       </c>
@@ -20787,8 +20795,8 @@
       <c r="K245" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L245" s="18" t="s">
-        <v>13</v>
+      <c r="L245" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M245" s="3">
         <v>18</v>
@@ -20821,7 +20829,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="246" spans="1:22">
+    <row r="246" spans="1:22" ht="14.4">
       <c r="A246" s="17" t="s">
         <v>623</v>
       </c>
@@ -20855,8 +20863,8 @@
       <c r="K246" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L246" s="18" t="s">
-        <v>13</v>
+      <c r="L246" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M246" s="3">
         <v>12</v>
@@ -20885,7 +20893,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="247" spans="1:22">
+    <row r="247" spans="1:22" ht="14.4">
       <c r="A247" s="17" t="s">
         <v>623</v>
       </c>
@@ -20919,8 +20927,8 @@
       <c r="K247" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L247" s="18" t="s">
-        <v>13</v>
+      <c r="L247" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M247" s="3">
         <v>12</v>
@@ -20953,7 +20961,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="248" spans="1:22" ht="15">
+    <row r="248" spans="1:22" ht="14.4">
       <c r="A248" s="17" t="s">
         <v>623</v>
       </c>
@@ -20987,8 +20995,8 @@
       <c r="K248" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L248" s="18" t="s">
-        <v>13</v>
+      <c r="L248" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M248" s="3">
         <v>12</v>
@@ -21021,7 +21029,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="249" spans="1:22">
+    <row r="249" spans="1:22" ht="14.4">
       <c r="A249" s="17" t="s">
         <v>623</v>
       </c>
@@ -21055,8 +21063,8 @@
       <c r="K249" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L249" s="18" t="s">
-        <v>13</v>
+      <c r="L249" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M249" s="3">
         <v>12</v>
@@ -21089,7 +21097,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="250" spans="1:22" ht="15">
+    <row r="250" spans="1:22" ht="14.4">
       <c r="A250" s="17" t="s">
         <v>626</v>
       </c>
@@ -21123,8 +21131,8 @@
       <c r="K250" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L250" s="18" t="s">
-        <v>13</v>
+      <c r="L250" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M250" s="3">
         <v>12</v>
@@ -21153,7 +21161,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="251" spans="1:22" ht="15">
+    <row r="251" spans="1:22" ht="14.4">
       <c r="A251" s="17" t="s">
         <v>626</v>
       </c>
@@ -21187,8 +21195,8 @@
       <c r="K251" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L251" s="18" t="s">
-        <v>13</v>
+      <c r="L251" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M251" s="3">
         <v>12</v>
@@ -21221,7 +21229,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="252" spans="1:22" ht="15">
+    <row r="252" spans="1:22" ht="14.4">
       <c r="A252" s="17" t="s">
         <v>626</v>
       </c>
@@ -21255,8 +21263,8 @@
       <c r="K252" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="L252" s="18" t="s">
-        <v>13</v>
+      <c r="L252" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M252" s="3">
         <v>12</v>
@@ -21289,7 +21297,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="253" spans="1:22" ht="15">
+    <row r="253" spans="1:22" ht="14.4">
       <c r="A253" s="22" t="s">
         <v>626</v>
       </c>
@@ -21323,8 +21331,8 @@
       <c r="K253" s="22" t="s">
         <v>775</v>
       </c>
-      <c r="L253" s="22" t="s">
-        <v>13</v>
+      <c r="L253" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M253" s="13">
         <v>12</v>
@@ -21357,7 +21365,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="254" spans="1:22">
+    <row r="254" spans="1:22" ht="14.4">
       <c r="A254" s="15" t="s">
         <v>629</v>
       </c>
@@ -21391,8 +21399,8 @@
       <c r="K254" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L254" s="31" t="s">
-        <v>13</v>
+      <c r="L254" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M254" s="13">
         <v>18</v>
@@ -21419,7 +21427,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="255" spans="1:22">
+    <row r="255" spans="1:22" ht="14.4">
       <c r="A255" s="15" t="s">
         <v>629</v>
       </c>
@@ -21453,8 +21461,8 @@
       <c r="K255" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L255" s="31" t="s">
-        <v>13</v>
+      <c r="L255" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M255" s="13">
         <v>18</v>
@@ -21485,7 +21493,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="256" spans="1:22">
+    <row r="256" spans="1:22" ht="14.4">
       <c r="A256" s="15" t="s">
         <v>629</v>
       </c>
@@ -21519,8 +21527,8 @@
       <c r="K256" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L256" s="31" t="s">
-        <v>13</v>
+      <c r="L256" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M256" s="13">
         <v>18</v>
@@ -21551,7 +21559,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="257" spans="1:22">
+    <row r="257" spans="1:22" ht="14.4">
       <c r="A257" s="15" t="s">
         <v>629</v>
       </c>
@@ -21585,8 +21593,8 @@
       <c r="K257" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L257" s="31" t="s">
-        <v>13</v>
+      <c r="L257" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M257" s="13">
         <v>18</v>
@@ -21619,7 +21627,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="258" spans="1:22">
+    <row r="258" spans="1:22" ht="14.4">
       <c r="A258" s="15" t="s">
         <v>631</v>
       </c>
@@ -21653,8 +21661,8 @@
       <c r="K258" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L258" s="31" t="s">
-        <v>13</v>
+      <c r="L258" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M258" s="13">
         <v>12</v>
@@ -21681,7 +21689,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="259" spans="1:22">
+    <row r="259" spans="1:22" ht="14.4">
       <c r="A259" s="15" t="s">
         <v>631</v>
       </c>
@@ -21715,8 +21723,8 @@
       <c r="K259" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L259" s="31" t="s">
-        <v>13</v>
+      <c r="L259" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M259" s="13">
         <v>12</v>
@@ -21747,7 +21755,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="260" spans="1:22">
+    <row r="260" spans="1:22" ht="14.4">
       <c r="A260" s="15" t="s">
         <v>631</v>
       </c>
@@ -21781,8 +21789,8 @@
       <c r="K260" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L260" s="31" t="s">
-        <v>13</v>
+      <c r="L260" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M260" s="13">
         <v>12</v>
@@ -21813,7 +21821,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="261" spans="1:22">
+    <row r="261" spans="1:22" ht="14.4">
       <c r="A261" s="15" t="s">
         <v>631</v>
       </c>
@@ -21847,8 +21855,8 @@
       <c r="K261" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L261" s="31" t="s">
-        <v>13</v>
+      <c r="L261" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M261" s="13">
         <v>12</v>
@@ -21881,7 +21889,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="262" spans="1:22">
+    <row r="262" spans="1:22" ht="14.4">
       <c r="A262" s="15" t="s">
         <v>636</v>
       </c>
@@ -21915,8 +21923,8 @@
       <c r="K262" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L262" s="31" t="s">
-        <v>13</v>
+      <c r="L262" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M262" s="13">
         <v>12</v>
@@ -21943,7 +21951,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="263" spans="1:22">
+    <row r="263" spans="1:22" ht="14.4">
       <c r="A263" s="15" t="s">
         <v>636</v>
       </c>
@@ -21977,8 +21985,8 @@
       <c r="K263" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L263" s="31" t="s">
-        <v>13</v>
+      <c r="L263" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M263" s="13">
         <v>12</v>
@@ -22009,7 +22017,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="264" spans="1:22">
+    <row r="264" spans="1:22" ht="14.4">
       <c r="A264" s="15" t="s">
         <v>636</v>
       </c>
@@ -22043,8 +22051,8 @@
       <c r="K264" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L264" s="31" t="s">
-        <v>13</v>
+      <c r="L264" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M264" s="13">
         <v>12</v>
@@ -22075,7 +22083,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="265" spans="1:22">
+    <row r="265" spans="1:22" ht="14.4">
       <c r="A265" s="15" t="s">
         <v>636</v>
       </c>
@@ -22109,8 +22117,8 @@
       <c r="K265" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L265" s="31" t="s">
-        <v>13</v>
+      <c r="L265" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M265" s="13">
         <v>12</v>
@@ -22143,7 +22151,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="266" spans="1:22">
+    <row r="266" spans="1:22" ht="14.4">
       <c r="A266" s="15" t="s">
         <v>639</v>
       </c>
@@ -22177,8 +22185,8 @@
       <c r="K266" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L266" s="31" t="s">
-        <v>13</v>
+      <c r="L266" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M266" s="13">
         <v>18</v>
@@ -22205,7 +22213,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="267" spans="1:22">
+    <row r="267" spans="1:22" ht="14.4">
       <c r="A267" s="15" t="s">
         <v>639</v>
       </c>
@@ -22239,8 +22247,8 @@
       <c r="K267" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L267" s="31" t="s">
-        <v>13</v>
+      <c r="L267" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M267" s="13">
         <v>18</v>
@@ -22271,7 +22279,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="268" spans="1:22">
+    <row r="268" spans="1:22" ht="14.4">
       <c r="A268" s="15" t="s">
         <v>639</v>
       </c>
@@ -22305,8 +22313,8 @@
       <c r="K268" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L268" s="31" t="s">
-        <v>13</v>
+      <c r="L268" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M268" s="13">
         <v>18</v>
@@ -22337,7 +22345,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="269" spans="1:22">
+    <row r="269" spans="1:22" ht="14.4">
       <c r="A269" s="15" t="s">
         <v>639</v>
       </c>
@@ -22371,8 +22379,8 @@
       <c r="K269" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L269" s="31" t="s">
-        <v>13</v>
+      <c r="L269" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M269" s="13">
         <v>18</v>
@@ -22405,7 +22413,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="270" spans="1:22">
+    <row r="270" spans="1:22" ht="14.4">
       <c r="A270" s="15" t="s">
         <v>642</v>
       </c>
@@ -22439,8 +22447,8 @@
       <c r="K270" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L270" s="31" t="s">
-        <v>13</v>
+      <c r="L270" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M270" s="13">
         <v>12</v>
@@ -22467,7 +22475,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="271" spans="1:22">
+    <row r="271" spans="1:22" ht="14.4">
       <c r="A271" s="15" t="s">
         <v>642</v>
       </c>
@@ -22501,8 +22509,8 @@
       <c r="K271" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L271" s="31" t="s">
-        <v>13</v>
+      <c r="L271" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M271" s="13">
         <v>12</v>
@@ -22533,7 +22541,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="272" spans="1:22">
+    <row r="272" spans="1:22" ht="14.4">
       <c r="A272" s="15" t="s">
         <v>642</v>
       </c>
@@ -22567,8 +22575,8 @@
       <c r="K272" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L272" s="31" t="s">
-        <v>13</v>
+      <c r="L272" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M272" s="13">
         <v>12</v>
@@ -22599,7 +22607,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="273" spans="1:22">
+    <row r="273" spans="1:22" ht="14.4">
       <c r="A273" s="15" t="s">
         <v>642</v>
       </c>
@@ -22633,8 +22641,8 @@
       <c r="K273" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L273" s="31" t="s">
-        <v>13</v>
+      <c r="L273" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M273" s="13">
         <v>12</v>
@@ -22667,7 +22675,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="274" spans="1:22">
+    <row r="274" spans="1:22" ht="14.4">
       <c r="A274" s="15" t="s">
         <v>644</v>
       </c>
@@ -22701,8 +22709,8 @@
       <c r="K274" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="L274" s="31" t="s">
-        <v>13</v>
+      <c r="L274" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M274" s="13">
         <v>12</v>
@@ -22729,7 +22737,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="275" spans="1:22">
+    <row r="275" spans="1:22" ht="14.4">
       <c r="A275" s="15" t="s">
         <v>644</v>
       </c>
@@ -22763,8 +22771,8 @@
       <c r="K275" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="L275" s="31" t="s">
-        <v>13</v>
+      <c r="L275" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M275" s="13">
         <v>12</v>
@@ -22795,7 +22803,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="276" spans="1:22">
+    <row r="276" spans="1:22" ht="14.4">
       <c r="A276" s="15" t="s">
         <v>644</v>
       </c>
@@ -22829,8 +22837,8 @@
       <c r="K276" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="L276" s="31" t="s">
-        <v>13</v>
+      <c r="L276" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M276" s="13">
         <v>12</v>
@@ -22861,7 +22869,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="277" spans="1:22">
+    <row r="277" spans="1:22" ht="14.4">
       <c r="A277" s="15" t="s">
         <v>644</v>
       </c>
@@ -22895,8 +22903,8 @@
       <c r="K277" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="L277" s="31" t="s">
-        <v>13</v>
+      <c r="L277" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M277" s="13">
         <v>12</v>
@@ -22929,7 +22937,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="278" spans="1:22">
+    <row r="278" spans="1:22" ht="14.4">
       <c r="A278" s="15" t="s">
         <v>648</v>
       </c>
@@ -22963,8 +22971,8 @@
       <c r="K278" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L278" s="31" t="s">
-        <v>13</v>
+      <c r="L278" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M278" s="13">
         <v>18</v>
@@ -22991,7 +22999,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="279" spans="1:22">
+    <row r="279" spans="1:22" ht="14.4">
       <c r="A279" s="15" t="s">
         <v>648</v>
       </c>
@@ -23025,8 +23033,8 @@
       <c r="K279" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L279" s="31" t="s">
-        <v>13</v>
+      <c r="L279" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M279" s="13">
         <v>18</v>
@@ -23057,7 +23065,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="280" spans="1:22">
+    <row r="280" spans="1:22" ht="14.4">
       <c r="A280" s="15" t="s">
         <v>648</v>
       </c>
@@ -23091,8 +23099,8 @@
       <c r="K280" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L280" s="31" t="s">
-        <v>13</v>
+      <c r="L280" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M280" s="13">
         <v>18</v>
@@ -23123,7 +23131,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="281" spans="1:22">
+    <row r="281" spans="1:22" ht="14.4">
       <c r="A281" s="15" t="s">
         <v>648</v>
       </c>
@@ -23157,8 +23165,8 @@
       <c r="K281" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L281" s="31" t="s">
-        <v>13</v>
+      <c r="L281" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M281" s="13">
         <v>18</v>
@@ -23191,7 +23199,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="282" spans="1:22">
+    <row r="282" spans="1:22" ht="14.4">
       <c r="A282" s="15" t="s">
         <v>651</v>
       </c>
@@ -23225,8 +23233,8 @@
       <c r="K282" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L282" s="31" t="s">
-        <v>13</v>
+      <c r="L282" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M282" s="13">
         <v>12</v>
@@ -23253,7 +23261,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="283" spans="1:22">
+    <row r="283" spans="1:22" ht="14.4">
       <c r="A283" s="15" t="s">
         <v>651</v>
       </c>
@@ -23287,8 +23295,8 @@
       <c r="K283" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L283" s="31" t="s">
-        <v>13</v>
+      <c r="L283" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M283" s="13">
         <v>12</v>
@@ -23319,7 +23327,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="284" spans="1:22">
+    <row r="284" spans="1:22" ht="14.4">
       <c r="A284" s="15" t="s">
         <v>651</v>
       </c>
@@ -23353,8 +23361,8 @@
       <c r="K284" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L284" s="31" t="s">
-        <v>13</v>
+      <c r="L284" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M284" s="13">
         <v>12</v>
@@ -23385,7 +23393,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="285" spans="1:22">
+    <row r="285" spans="1:22" ht="14.4">
       <c r="A285" s="15" t="s">
         <v>651</v>
       </c>
@@ -23419,8 +23427,8 @@
       <c r="K285" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L285" s="31" t="s">
-        <v>13</v>
+      <c r="L285" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M285" s="13">
         <v>12</v>
@@ -23453,7 +23461,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="286" spans="1:22">
+    <row r="286" spans="1:22" ht="14.4">
       <c r="A286" s="15" t="s">
         <v>654</v>
       </c>
@@ -23487,8 +23495,8 @@
       <c r="K286" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L286" s="31" t="s">
-        <v>13</v>
+      <c r="L286" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M286" s="13">
         <v>12</v>
@@ -23515,7 +23523,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="287" spans="1:22">
+    <row r="287" spans="1:22" ht="14.4">
       <c r="A287" s="15" t="s">
         <v>654</v>
       </c>
@@ -23549,8 +23557,8 @@
       <c r="K287" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L287" s="31" t="s">
-        <v>13</v>
+      <c r="L287" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M287" s="13">
         <v>12</v>
@@ -23581,7 +23589,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="288" spans="1:22">
+    <row r="288" spans="1:22" ht="14.4">
       <c r="A288" s="15" t="s">
         <v>654</v>
       </c>
@@ -23615,8 +23623,8 @@
       <c r="K288" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L288" s="31" t="s">
-        <v>13</v>
+      <c r="L288" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M288" s="13">
         <v>12</v>
@@ -23647,7 +23655,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="289" spans="1:22">
+    <row r="289" spans="1:22" ht="14.4">
       <c r="A289" s="15" t="s">
         <v>654</v>
       </c>
@@ -23681,8 +23689,8 @@
       <c r="K289" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L289" s="31" t="s">
-        <v>13</v>
+      <c r="L289" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M289" s="13">
         <v>12</v>
@@ -23715,7 +23723,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="290" spans="1:22">
+    <row r="290" spans="1:22" ht="14.4">
       <c r="A290" s="15" t="s">
         <v>211</v>
       </c>
@@ -23749,8 +23757,8 @@
       <c r="K290" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="L290" s="31" t="s">
-        <v>13</v>
+      <c r="L290" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M290" s="13">
         <v>12</v>
@@ -23777,7 +23785,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="291" spans="1:22">
+    <row r="291" spans="1:22" ht="14.4">
       <c r="A291" s="15" t="s">
         <v>211</v>
       </c>
@@ -23811,8 +23819,8 @@
       <c r="K291" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="L291" s="31" t="s">
-        <v>13</v>
+      <c r="L291" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M291" s="13">
         <v>12</v>
@@ -23843,7 +23851,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="292" spans="1:22">
+    <row r="292" spans="1:22" ht="14.4">
       <c r="A292" s="15" t="s">
         <v>211</v>
       </c>
@@ -23877,8 +23885,8 @@
       <c r="K292" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="L292" s="31" t="s">
-        <v>13</v>
+      <c r="L292" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M292" s="13">
         <v>12</v>
@@ -23909,7 +23917,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="293" spans="1:22">
+    <row r="293" spans="1:22" ht="14.4">
       <c r="A293" s="15" t="s">
         <v>211</v>
       </c>
@@ -23943,8 +23951,8 @@
       <c r="K293" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="L293" s="31" t="s">
-        <v>13</v>
+      <c r="L293" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M293" s="13">
         <v>12</v>
@@ -23977,7 +23985,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="294" spans="1:22">
+    <row r="294" spans="1:22" ht="14.4">
       <c r="A294" s="15" t="s">
         <v>381</v>
       </c>
@@ -24011,8 +24019,8 @@
       <c r="K294" s="31" t="s">
         <v>809</v>
       </c>
-      <c r="L294" s="31" t="s">
-        <v>13</v>
+      <c r="L294" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M294" s="13">
         <v>24</v>
@@ -24039,7 +24047,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="295" spans="1:22">
+    <row r="295" spans="1:22" ht="14.4">
       <c r="A295" s="15" t="s">
         <v>381</v>
       </c>
@@ -24073,8 +24081,8 @@
       <c r="K295" s="31" t="s">
         <v>809</v>
       </c>
-      <c r="L295" s="31" t="s">
-        <v>13</v>
+      <c r="L295" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M295" s="13">
         <v>24</v>
@@ -24105,7 +24113,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="296" spans="1:22">
+    <row r="296" spans="1:22" ht="14.4">
       <c r="A296" s="15" t="s">
         <v>381</v>
       </c>
@@ -24139,8 +24147,8 @@
       <c r="K296" s="31" t="s">
         <v>809</v>
       </c>
-      <c r="L296" s="31" t="s">
-        <v>13</v>
+      <c r="L296" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M296" s="13">
         <v>24</v>
@@ -24171,7 +24179,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="297" spans="1:22">
+    <row r="297" spans="1:22" ht="14.4">
       <c r="A297" s="15" t="s">
         <v>381</v>
       </c>
@@ -24205,8 +24213,8 @@
       <c r="K297" s="31" t="s">
         <v>809</v>
       </c>
-      <c r="L297" s="31" t="s">
-        <v>13</v>
+      <c r="L297" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M297" s="13">
         <v>24</v>
@@ -24239,7 +24247,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="298" spans="1:22">
+    <row r="298" spans="1:22" ht="14.4">
       <c r="A298" s="15" t="s">
         <v>382</v>
       </c>
@@ -24273,8 +24281,8 @@
       <c r="K298" s="31" t="s">
         <v>827</v>
       </c>
-      <c r="L298" s="31" t="s">
-        <v>13</v>
+      <c r="L298" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M298" s="13">
         <v>6</v>
@@ -24301,7 +24309,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="299" spans="1:22">
+    <row r="299" spans="1:22" ht="14.4">
       <c r="A299" s="15" t="s">
         <v>382</v>
       </c>
@@ -24335,8 +24343,8 @@
       <c r="K299" s="31" t="s">
         <v>827</v>
       </c>
-      <c r="L299" s="31" t="s">
-        <v>13</v>
+      <c r="L299" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M299" s="13">
         <v>6</v>
@@ -24367,7 +24375,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="300" spans="1:22">
+    <row r="300" spans="1:22" ht="14.4">
       <c r="A300" s="15" t="s">
         <v>382</v>
       </c>
@@ -24401,8 +24409,8 @@
       <c r="K300" s="31" t="s">
         <v>827</v>
       </c>
-      <c r="L300" s="31" t="s">
-        <v>13</v>
+      <c r="L300" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M300" s="13">
         <v>6</v>
@@ -24433,7 +24441,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="301" spans="1:22">
+    <row r="301" spans="1:22" ht="14.4">
       <c r="A301" s="15" t="s">
         <v>382</v>
       </c>
@@ -24467,8 +24475,8 @@
       <c r="K301" s="31" t="s">
         <v>827</v>
       </c>
-      <c r="L301" s="31" t="s">
-        <v>13</v>
+      <c r="L301" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M301" s="13">
         <v>6</v>
@@ -24501,7 +24509,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="302" spans="1:22">
+    <row r="302" spans="1:22" ht="14.4">
       <c r="A302" s="15" t="s">
         <v>383</v>
       </c>
@@ -24535,8 +24543,8 @@
       <c r="K302" s="31" t="s">
         <v>894</v>
       </c>
-      <c r="L302" s="31" t="s">
-        <v>13</v>
+      <c r="L302" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M302" s="13">
         <v>18</v>
@@ -24563,7 +24571,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="303" spans="1:22">
+    <row r="303" spans="1:22" ht="14.4">
       <c r="A303" s="15" t="s">
         <v>383</v>
       </c>
@@ -24597,8 +24605,8 @@
       <c r="K303" s="31" t="s">
         <v>894</v>
       </c>
-      <c r="L303" s="31" t="s">
-        <v>13</v>
+      <c r="L303" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M303" s="13">
         <v>18</v>
@@ -24629,7 +24637,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="304" spans="1:22">
+    <row r="304" spans="1:22" ht="14.4">
       <c r="A304" s="15" t="s">
         <v>383</v>
       </c>
@@ -24663,8 +24671,8 @@
       <c r="K304" s="31" t="s">
         <v>894</v>
       </c>
-      <c r="L304" s="31" t="s">
-        <v>13</v>
+      <c r="L304" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M304" s="13">
         <v>18</v>
@@ -24695,7 +24703,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="305" spans="1:22">
+    <row r="305" spans="1:22" ht="14.4">
       <c r="A305" s="15" t="s">
         <v>383</v>
       </c>
@@ -24729,8 +24737,8 @@
       <c r="K305" s="31" t="s">
         <v>894</v>
       </c>
-      <c r="L305" s="31" t="s">
-        <v>13</v>
+      <c r="L305" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M305" s="13">
         <v>18</v>
@@ -24763,7 +24771,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="306" spans="1:22">
+    <row r="306" spans="1:22" ht="14.4">
       <c r="A306" s="15" t="s">
         <v>384</v>
       </c>
@@ -24797,8 +24805,8 @@
       <c r="K306" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="L306" s="31" t="s">
-        <v>13</v>
+      <c r="L306" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M306" s="13">
         <v>12</v>
@@ -24825,7 +24833,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="307" spans="1:22">
+    <row r="307" spans="1:22" ht="14.4">
       <c r="A307" s="15" t="s">
         <v>384</v>
       </c>
@@ -24859,8 +24867,8 @@
       <c r="K307" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="L307" s="31" t="s">
-        <v>13</v>
+      <c r="L307" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M307" s="13">
         <v>12</v>
@@ -24891,7 +24899,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="308" spans="1:22">
+    <row r="308" spans="1:22" ht="14.4">
       <c r="A308" s="15" t="s">
         <v>384</v>
       </c>
@@ -24925,8 +24933,8 @@
       <c r="K308" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="L308" s="31" t="s">
-        <v>13</v>
+      <c r="L308" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M308" s="13">
         <v>12</v>
@@ -24957,7 +24965,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="309" spans="1:22">
+    <row r="309" spans="1:22" ht="14.4">
       <c r="A309" s="15" t="s">
         <v>384</v>
       </c>
@@ -24991,8 +24999,8 @@
       <c r="K309" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="L309" s="31" t="s">
-        <v>13</v>
+      <c r="L309" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M309" s="13">
         <v>12</v>
@@ -25025,7 +25033,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="310" spans="1:22">
+    <row r="310" spans="1:22" ht="14.4">
       <c r="A310" s="15" t="s">
         <v>387</v>
       </c>
@@ -25059,8 +25067,8 @@
       <c r="K310" s="31" t="s">
         <v>904</v>
       </c>
-      <c r="L310" s="31" t="s">
-        <v>13</v>
+      <c r="L310" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M310" s="13">
         <v>12</v>
@@ -25087,7 +25095,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="311" spans="1:22">
+    <row r="311" spans="1:22" ht="14.4">
       <c r="A311" s="15" t="s">
         <v>387</v>
       </c>
@@ -25121,8 +25129,8 @@
       <c r="K311" s="31" t="s">
         <v>904</v>
       </c>
-      <c r="L311" s="31" t="s">
-        <v>13</v>
+      <c r="L311" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M311" s="13">
         <v>12</v>
@@ -25153,7 +25161,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="312" spans="1:22">
+    <row r="312" spans="1:22" ht="14.4">
       <c r="A312" s="15" t="s">
         <v>387</v>
       </c>
@@ -25187,8 +25195,8 @@
       <c r="K312" s="31" t="s">
         <v>904</v>
       </c>
-      <c r="L312" s="31" t="s">
-        <v>13</v>
+      <c r="L312" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M312" s="13">
         <v>12</v>
@@ -25219,7 +25227,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="313" spans="1:22">
+    <row r="313" spans="1:22" ht="14.4">
       <c r="A313" s="15" t="s">
         <v>387</v>
       </c>
@@ -25253,8 +25261,8 @@
       <c r="K313" s="31" t="s">
         <v>904</v>
       </c>
-      <c r="L313" s="31" t="s">
-        <v>13</v>
+      <c r="L313" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M313" s="13">
         <v>12</v>
@@ -25287,7 +25295,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="314" spans="1:22">
+    <row r="314" spans="1:22" ht="14.4">
       <c r="A314" s="15" t="s">
         <v>388</v>
       </c>
@@ -25321,8 +25329,8 @@
       <c r="K314" s="31" t="s">
         <v>910</v>
       </c>
-      <c r="L314" s="31" t="s">
-        <v>13</v>
+      <c r="L314" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M314" s="13">
         <v>24</v>
@@ -25349,7 +25357,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="315" spans="1:22">
+    <row r="315" spans="1:22" ht="14.4">
       <c r="A315" s="15" t="s">
         <v>388</v>
       </c>
@@ -25383,8 +25391,8 @@
       <c r="K315" s="31" t="s">
         <v>910</v>
       </c>
-      <c r="L315" s="31" t="s">
-        <v>13</v>
+      <c r="L315" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M315" s="13">
         <v>24</v>
@@ -25415,7 +25423,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="316" spans="1:22">
+    <row r="316" spans="1:22" ht="14.4">
       <c r="A316" s="15" t="s">
         <v>388</v>
       </c>
@@ -25449,8 +25457,8 @@
       <c r="K316" s="31" t="s">
         <v>910</v>
       </c>
-      <c r="L316" s="31" t="s">
-        <v>13</v>
+      <c r="L316" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M316" s="13">
         <v>24</v>
@@ -25481,7 +25489,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="317" spans="1:22">
+    <row r="317" spans="1:22" ht="14.4">
       <c r="A317" s="15" t="s">
         <v>388</v>
       </c>
@@ -25515,8 +25523,8 @@
       <c r="K317" s="31" t="s">
         <v>910</v>
       </c>
-      <c r="L317" s="31" t="s">
-        <v>13</v>
+      <c r="L317" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M317" s="13">
         <v>24</v>
@@ -25549,7 +25557,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="318" spans="1:22">
+    <row r="318" spans="1:22" ht="14.4">
       <c r="A318" s="15" t="s">
         <v>389</v>
       </c>
@@ -25583,8 +25591,8 @@
       <c r="K318" s="31" t="s">
         <v>914</v>
       </c>
-      <c r="L318" s="31" t="s">
-        <v>13</v>
+      <c r="L318" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M318" s="13">
         <v>6</v>
@@ -25611,7 +25619,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="319" spans="1:22">
+    <row r="319" spans="1:22" ht="14.4">
       <c r="A319" s="15" t="s">
         <v>389</v>
       </c>
@@ -25645,8 +25653,8 @@
       <c r="K319" s="31" t="s">
         <v>914</v>
       </c>
-      <c r="L319" s="31" t="s">
-        <v>13</v>
+      <c r="L319" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M319" s="13">
         <v>6</v>
@@ -25677,7 +25685,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="320" spans="1:22">
+    <row r="320" spans="1:22" ht="14.4">
       <c r="A320" s="15" t="s">
         <v>389</v>
       </c>
@@ -25711,8 +25719,8 @@
       <c r="K320" s="31" t="s">
         <v>914</v>
       </c>
-      <c r="L320" s="31" t="s">
-        <v>13</v>
+      <c r="L320" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M320" s="13">
         <v>6</v>
@@ -25743,7 +25751,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="321" spans="1:22">
+    <row r="321" spans="1:22" ht="14.4">
       <c r="A321" s="15" t="s">
         <v>389</v>
       </c>
@@ -25777,8 +25785,8 @@
       <c r="K321" s="31" t="s">
         <v>914</v>
       </c>
-      <c r="L321" s="31" t="s">
-        <v>13</v>
+      <c r="L321" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M321" s="13">
         <v>6</v>
@@ -25811,7 +25819,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="322" spans="1:22">
+    <row r="322" spans="1:22" ht="14.4">
       <c r="A322" s="15" t="s">
         <v>392</v>
       </c>
@@ -25845,8 +25853,8 @@
       <c r="K322" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="L322" s="31" t="s">
-        <v>13</v>
+      <c r="L322" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M322" s="13">
         <v>18</v>
@@ -25873,7 +25881,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="323" spans="1:22">
+    <row r="323" spans="1:22" ht="14.4">
       <c r="A323" s="15" t="s">
         <v>392</v>
       </c>
@@ -25907,8 +25915,8 @@
       <c r="K323" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="L323" s="31" t="s">
-        <v>13</v>
+      <c r="L323" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M323" s="13">
         <v>18</v>
@@ -25939,7 +25947,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="324" spans="1:22">
+    <row r="324" spans="1:22" ht="14.4">
       <c r="A324" s="15" t="s">
         <v>392</v>
       </c>
@@ -25973,8 +25981,8 @@
       <c r="K324" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="L324" s="31" t="s">
-        <v>13</v>
+      <c r="L324" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M324" s="13">
         <v>18</v>
@@ -26005,7 +26013,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="325" spans="1:22">
+    <row r="325" spans="1:22" ht="14.4">
       <c r="A325" s="15" t="s">
         <v>392</v>
       </c>
@@ -26039,8 +26047,8 @@
       <c r="K325" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="L325" s="31" t="s">
-        <v>13</v>
+      <c r="L325" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M325" s="13">
         <v>18</v>
@@ -26073,7 +26081,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="326" spans="1:22">
+    <row r="326" spans="1:22" ht="14.4">
       <c r="A326" s="15" t="s">
         <v>395</v>
       </c>
@@ -26107,8 +26115,8 @@
       <c r="K326" s="31" t="s">
         <v>809</v>
       </c>
-      <c r="L326" s="31" t="s">
-        <v>13</v>
+      <c r="L326" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M326" s="13">
         <v>12</v>
@@ -26135,7 +26143,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="327" spans="1:22">
+    <row r="327" spans="1:22" ht="14.4">
       <c r="A327" s="15" t="s">
         <v>395</v>
       </c>
@@ -26169,8 +26177,8 @@
       <c r="K327" s="31" t="s">
         <v>809</v>
       </c>
-      <c r="L327" s="31" t="s">
-        <v>13</v>
+      <c r="L327" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M327" s="13">
         <v>12</v>
@@ -26201,7 +26209,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="328" spans="1:22">
+    <row r="328" spans="1:22" ht="14.4">
       <c r="A328" s="15" t="s">
         <v>395</v>
       </c>
@@ -26235,8 +26243,8 @@
       <c r="K328" s="31" t="s">
         <v>809</v>
       </c>
-      <c r="L328" s="31" t="s">
-        <v>13</v>
+      <c r="L328" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M328" s="13">
         <v>12</v>
@@ -26267,7 +26275,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="329" spans="1:22">
+    <row r="329" spans="1:22" ht="14.4">
       <c r="A329" s="15" t="s">
         <v>395</v>
       </c>
@@ -26301,8 +26309,8 @@
       <c r="K329" s="31" t="s">
         <v>809</v>
       </c>
-      <c r="L329" s="31" t="s">
-        <v>13</v>
+      <c r="L329" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M329" s="13">
         <v>12</v>
@@ -26335,7 +26343,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="330" spans="1:22">
+    <row r="330" spans="1:22" ht="14.4">
       <c r="A330" s="15" t="s">
         <v>396</v>
       </c>
@@ -26369,8 +26377,8 @@
       <c r="K330" s="31" t="s">
         <v>809</v>
       </c>
-      <c r="L330" s="31" t="s">
-        <v>13</v>
+      <c r="L330" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M330" s="13">
         <v>12</v>
@@ -26397,7 +26405,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="331" spans="1:22">
+    <row r="331" spans="1:22" ht="14.4">
       <c r="A331" s="15" t="s">
         <v>396</v>
       </c>
@@ -26431,8 +26439,8 @@
       <c r="K331" s="31" t="s">
         <v>809</v>
       </c>
-      <c r="L331" s="31" t="s">
-        <v>13</v>
+      <c r="L331" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M331" s="13">
         <v>12</v>
@@ -26463,7 +26471,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="332" spans="1:22">
+    <row r="332" spans="1:22" ht="14.4">
       <c r="A332" s="15" t="s">
         <v>396</v>
       </c>
@@ -26497,8 +26505,8 @@
       <c r="K332" s="31" t="s">
         <v>809</v>
       </c>
-      <c r="L332" s="31" t="s">
-        <v>13</v>
+      <c r="L332" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M332" s="13">
         <v>12</v>
@@ -26529,7 +26537,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="333" spans="1:22">
+    <row r="333" spans="1:22" ht="14.4">
       <c r="A333" s="15" t="s">
         <v>396</v>
       </c>
@@ -26563,8 +26571,8 @@
       <c r="K333" s="31" t="s">
         <v>809</v>
       </c>
-      <c r="L333" s="31" t="s">
-        <v>13</v>
+      <c r="L333" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M333" s="13">
         <v>12</v>
@@ -26597,7 +26605,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="334" spans="1:22">
+    <row r="334" spans="1:22" ht="14.4">
       <c r="A334" s="15" t="s">
         <v>397</v>
       </c>
@@ -26631,8 +26639,8 @@
       <c r="K334" s="31" t="s">
         <v>853</v>
       </c>
-      <c r="L334" s="31" t="s">
-        <v>13</v>
+      <c r="L334" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M334" s="13">
         <v>24</v>
@@ -26659,7 +26667,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="335" spans="1:22">
+    <row r="335" spans="1:22" ht="14.4">
       <c r="A335" s="15" t="s">
         <v>397</v>
       </c>
@@ -26693,8 +26701,8 @@
       <c r="K335" s="31" t="s">
         <v>853</v>
       </c>
-      <c r="L335" s="31" t="s">
-        <v>13</v>
+      <c r="L335" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M335" s="13">
         <v>24</v>
@@ -26725,7 +26733,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="336" spans="1:22">
+    <row r="336" spans="1:22" ht="14.4">
       <c r="A336" s="15" t="s">
         <v>397</v>
       </c>
@@ -26759,8 +26767,8 @@
       <c r="K336" s="31" t="s">
         <v>853</v>
       </c>
-      <c r="L336" s="31" t="s">
-        <v>13</v>
+      <c r="L336" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M336" s="13">
         <v>24</v>
@@ -26791,7 +26799,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="337" spans="1:22">
+    <row r="337" spans="1:22" ht="14.4">
       <c r="A337" s="15" t="s">
         <v>397</v>
       </c>
@@ -26825,8 +26833,8 @@
       <c r="K337" s="31" t="s">
         <v>853</v>
       </c>
-      <c r="L337" s="31" t="s">
-        <v>13</v>
+      <c r="L337" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M337" s="13">
         <v>24</v>
@@ -26859,7 +26867,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="338" spans="1:22">
+    <row r="338" spans="1:22" ht="14.4">
       <c r="A338" s="15" t="s">
         <v>398</v>
       </c>
@@ -26893,8 +26901,8 @@
       <c r="K338" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L338" s="31" t="s">
-        <v>13</v>
+      <c r="L338" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M338" s="13">
         <v>6</v>
@@ -26927,7 +26935,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="339" spans="1:22">
+    <row r="339" spans="1:22" ht="14.4">
       <c r="A339" s="15" t="s">
         <v>398</v>
       </c>
@@ -26961,8 +26969,8 @@
       <c r="K339" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L339" s="31" t="s">
-        <v>13</v>
+      <c r="L339" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M339" s="13">
         <v>6</v>
@@ -26995,7 +27003,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="340" spans="1:22">
+    <row r="340" spans="1:22" ht="14.4">
       <c r="A340" s="15" t="s">
         <v>398</v>
       </c>
@@ -27029,8 +27037,8 @@
       <c r="K340" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L340" s="31" t="s">
-        <v>13</v>
+      <c r="L340" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M340" s="13">
         <v>6</v>
@@ -27063,7 +27071,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="341" spans="1:22">
+    <row r="341" spans="1:22" ht="14.4">
       <c r="A341" s="15" t="s">
         <v>398</v>
       </c>
@@ -27097,8 +27105,8 @@
       <c r="K341" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L341" s="31" t="s">
-        <v>13</v>
+      <c r="L341" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M341" s="13">
         <v>6</v>
@@ -27131,7 +27139,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="342" spans="1:22">
+    <row r="342" spans="1:22" ht="14.4">
       <c r="A342" s="15" t="s">
         <v>400</v>
       </c>
@@ -27165,8 +27173,8 @@
       <c r="K342" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L342" s="31" t="s">
-        <v>13</v>
+      <c r="L342" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M342" s="13">
         <v>18</v>
@@ -27199,7 +27207,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="343" spans="1:22">
+    <row r="343" spans="1:22" ht="14.4">
       <c r="A343" s="15" t="s">
         <v>400</v>
       </c>
@@ -27233,8 +27241,8 @@
       <c r="K343" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L343" s="31" t="s">
-        <v>13</v>
+      <c r="L343" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M343" s="13">
         <v>18</v>
@@ -27267,7 +27275,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="344" spans="1:22">
+    <row r="344" spans="1:22" ht="14.4">
       <c r="A344" s="15" t="s">
         <v>400</v>
       </c>
@@ -27301,8 +27309,8 @@
       <c r="K344" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L344" s="31" t="s">
-        <v>13</v>
+      <c r="L344" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M344" s="13">
         <v>18</v>
@@ -27335,7 +27343,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="345" spans="1:22">
+    <row r="345" spans="1:22" ht="14.4">
       <c r="A345" s="15" t="s">
         <v>400</v>
       </c>
@@ -27369,8 +27377,8 @@
       <c r="K345" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L345" s="31" t="s">
-        <v>13</v>
+      <c r="L345" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M345" s="13">
         <v>18</v>
@@ -27403,7 +27411,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="346" spans="1:22">
+    <row r="346" spans="1:22" ht="14.4">
       <c r="A346" s="15" t="s">
         <v>403</v>
       </c>
@@ -27437,8 +27445,8 @@
       <c r="K346" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L346" s="31" t="s">
-        <v>13</v>
+      <c r="L346" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M346" s="13">
         <v>12</v>
@@ -27471,7 +27479,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="347" spans="1:22">
+    <row r="347" spans="1:22" ht="14.4">
       <c r="A347" s="15" t="s">
         <v>403</v>
       </c>
@@ -27505,8 +27513,8 @@
       <c r="K347" s="31" t="s">
         <v>775</v>
       </c>
-      <c r="L347" s="31" t="s">
-        <v>13</v>
+      <c r="L347" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M347" s="13">
         <v>12</v>
@@ -27539,7 +27547,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="348" spans="1:22">
+    <row r="348" spans="1:22" ht="14.4">
       <c r="A348" s="15" t="s">
         <v>403</v>
       </c>
@@ -27573,8 +27581,8 @@
       <c r="K348" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L348" s="29" t="s">
-        <v>13</v>
+      <c r="L348" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M348" s="27">
         <v>12</v>
@@ -27605,7 +27613,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="349" spans="1:22">
+    <row r="349" spans="1:22" ht="14.4">
       <c r="A349" s="15" t="s">
         <v>403</v>
       </c>
@@ -27639,8 +27647,8 @@
       <c r="K349" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L349" s="29" t="s">
-        <v>13</v>
+      <c r="L349" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M349" s="27">
         <v>12</v>
@@ -27673,7 +27681,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="350" spans="1:22">
+    <row r="350" spans="1:22" ht="14.4">
       <c r="A350" s="15" t="s">
         <v>406</v>
       </c>
@@ -27707,8 +27715,8 @@
       <c r="K350" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L350" s="29" t="s">
-        <v>13</v>
+      <c r="L350" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M350" s="27">
         <v>12</v>
@@ -27739,7 +27747,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="351" spans="1:22">
+    <row r="351" spans="1:22" ht="14.4">
       <c r="A351" s="15" t="s">
         <v>406</v>
       </c>
@@ -27773,8 +27781,8 @@
       <c r="K351" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L351" s="29" t="s">
-        <v>13</v>
+      <c r="L351" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M351" s="27">
         <v>12</v>
@@ -27807,7 +27815,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="352" spans="1:22">
+    <row r="352" spans="1:22" ht="14.4">
       <c r="A352" s="15" t="s">
         <v>406</v>
       </c>
@@ -27841,8 +27849,8 @@
       <c r="K352" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L352" s="29" t="s">
-        <v>13</v>
+      <c r="L352" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M352" s="27">
         <v>12</v>
@@ -27873,7 +27881,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="353" spans="1:22">
+    <row r="353" spans="1:22" ht="14.4">
       <c r="A353" s="15" t="s">
         <v>406</v>
       </c>
@@ -27907,8 +27915,8 @@
       <c r="K353" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L353" s="29" t="s">
-        <v>13</v>
+      <c r="L353" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M353" s="27">
         <v>12</v>
@@ -27941,7 +27949,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="354" spans="1:22">
+    <row r="354" spans="1:22" ht="14.4">
       <c r="A354" s="15" t="s">
         <v>409</v>
       </c>
@@ -27975,8 +27983,8 @@
       <c r="K354" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L354" s="29" t="s">
-        <v>13</v>
+      <c r="L354" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M354" s="27">
         <v>24</v>
@@ -28007,7 +28015,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="355" spans="1:22">
+    <row r="355" spans="1:22" ht="14.4">
       <c r="A355" s="15" t="s">
         <v>409</v>
       </c>
@@ -28041,8 +28049,8 @@
       <c r="K355" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L355" s="29" t="s">
-        <v>13</v>
+      <c r="L355" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M355" s="27">
         <v>24</v>
@@ -28075,7 +28083,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="356" spans="1:22">
+    <row r="356" spans="1:22" ht="14.4">
       <c r="A356" s="15" t="s">
         <v>409</v>
       </c>
@@ -28109,8 +28117,8 @@
       <c r="K356" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L356" s="29" t="s">
-        <v>13</v>
+      <c r="L356" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M356" s="27">
         <v>24</v>
@@ -28141,7 +28149,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="357" spans="1:22">
+    <row r="357" spans="1:22" ht="14.4">
       <c r="A357" s="15" t="s">
         <v>409</v>
       </c>
@@ -28175,8 +28183,8 @@
       <c r="K357" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L357" s="29" t="s">
-        <v>13</v>
+      <c r="L357" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M357" s="27">
         <v>24</v>
@@ -28209,7 +28217,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="358" spans="1:22">
+    <row r="358" spans="1:22" ht="14.4">
       <c r="A358" s="15" t="s">
         <v>411</v>
       </c>
@@ -28243,8 +28251,8 @@
       <c r="K358" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L358" s="29" t="s">
-        <v>13</v>
+      <c r="L358" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M358" s="27">
         <v>6</v>
@@ -28275,7 +28283,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="359" spans="1:22">
+    <row r="359" spans="1:22" ht="14.4">
       <c r="A359" s="15" t="s">
         <v>411</v>
       </c>
@@ -28309,8 +28317,8 @@
       <c r="K359" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L359" s="29" t="s">
-        <v>13</v>
+      <c r="L359" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M359" s="27">
         <v>6</v>
@@ -28343,7 +28351,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="360" spans="1:22">
+    <row r="360" spans="1:22" ht="14.4">
       <c r="A360" s="15" t="s">
         <v>411</v>
       </c>
@@ -28377,8 +28385,8 @@
       <c r="K360" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L360" s="29" t="s">
-        <v>13</v>
+      <c r="L360" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M360" s="27">
         <v>6</v>
@@ -28409,7 +28417,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="361" spans="1:22">
+    <row r="361" spans="1:22" ht="14.4">
       <c r="A361" s="15" t="s">
         <v>411</v>
       </c>
@@ -28443,8 +28451,8 @@
       <c r="K361" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L361" s="29" t="s">
-        <v>13</v>
+      <c r="L361" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M361" s="27">
         <v>6</v>
@@ -28477,7 +28485,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="362" spans="1:22">
+    <row r="362" spans="1:22" ht="14.4">
       <c r="A362" s="15" t="s">
         <v>414</v>
       </c>
@@ -28511,8 +28519,8 @@
       <c r="K362" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L362" s="29" t="s">
-        <v>13</v>
+      <c r="L362" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M362" s="27">
         <v>18</v>
@@ -28543,7 +28551,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="363" spans="1:22">
+    <row r="363" spans="1:22" ht="14.4">
       <c r="A363" s="15" t="s">
         <v>414</v>
       </c>
@@ -28577,8 +28585,8 @@
       <c r="K363" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L363" s="29" t="s">
-        <v>13</v>
+      <c r="L363" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M363" s="27">
         <v>18</v>
@@ -28611,7 +28619,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="364" spans="1:22">
+    <row r="364" spans="1:22" ht="14.4">
       <c r="A364" s="15" t="s">
         <v>414</v>
       </c>
@@ -28645,8 +28653,8 @@
       <c r="K364" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L364" s="29" t="s">
-        <v>13</v>
+      <c r="L364" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M364" s="27">
         <v>18</v>
@@ -28677,7 +28685,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="365" spans="1:22">
+    <row r="365" spans="1:22" ht="14.4">
       <c r="A365" s="15" t="s">
         <v>414</v>
       </c>
@@ -28711,8 +28719,8 @@
       <c r="K365" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L365" s="29" t="s">
-        <v>13</v>
+      <c r="L365" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M365" s="27">
         <v>18</v>
@@ -28745,7 +28753,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="366" spans="1:22">
+    <row r="366" spans="1:22" ht="14.4">
       <c r="A366" s="15" t="s">
         <v>417</v>
       </c>
@@ -28779,8 +28787,8 @@
       <c r="K366" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L366" s="29" t="s">
-        <v>13</v>
+      <c r="L366" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M366" s="27">
         <v>12</v>
@@ -28811,7 +28819,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="367" spans="1:22">
+    <row r="367" spans="1:22" ht="14.4">
       <c r="A367" s="15" t="s">
         <v>417</v>
       </c>
@@ -28845,8 +28853,8 @@
       <c r="K367" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L367" s="29" t="s">
-        <v>13</v>
+      <c r="L367" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M367" s="27">
         <v>12</v>
@@ -28879,7 +28887,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="368" spans="1:22">
+    <row r="368" spans="1:22" ht="14.4">
       <c r="A368" s="15" t="s">
         <v>417</v>
       </c>
@@ -28913,8 +28921,8 @@
       <c r="K368" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L368" s="29" t="s">
-        <v>13</v>
+      <c r="L368" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M368" s="27">
         <v>12</v>
@@ -28945,7 +28953,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="369" spans="1:22">
+    <row r="369" spans="1:22" ht="14.4">
       <c r="A369" s="15" t="s">
         <v>417</v>
       </c>
@@ -28979,8 +28987,8 @@
       <c r="K369" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L369" s="29" t="s">
-        <v>13</v>
+      <c r="L369" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M369" s="27">
         <v>12</v>
@@ -29013,7 +29021,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="370" spans="1:22">
+    <row r="370" spans="1:22" ht="14.4">
       <c r="A370" s="15" t="s">
         <v>420</v>
       </c>
@@ -29047,8 +29055,8 @@
       <c r="K370" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L370" s="29" t="s">
-        <v>13</v>
+      <c r="L370" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M370" s="27">
         <v>12</v>
@@ -29079,7 +29087,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="371" spans="1:22">
+    <row r="371" spans="1:22" ht="14.4">
       <c r="A371" s="15" t="s">
         <v>420</v>
       </c>
@@ -29113,8 +29121,8 @@
       <c r="K371" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L371" s="29" t="s">
-        <v>13</v>
+      <c r="L371" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M371" s="27">
         <v>12</v>
@@ -29147,7 +29155,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="372" spans="1:22">
+    <row r="372" spans="1:22" ht="14.4">
       <c r="A372" s="15" t="s">
         <v>420</v>
       </c>
@@ -29181,8 +29189,8 @@
       <c r="K372" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L372" s="29" t="s">
-        <v>13</v>
+      <c r="L372" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M372" s="27">
         <v>12</v>
@@ -29213,7 +29221,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="373" spans="1:22">
+    <row r="373" spans="1:22" ht="14.4">
       <c r="A373" s="15" t="s">
         <v>420</v>
       </c>
@@ -29247,8 +29255,8 @@
       <c r="K373" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L373" s="29" t="s">
-        <v>13</v>
+      <c r="L373" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M373" s="27">
         <v>12</v>
@@ -29281,7 +29289,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="374" spans="1:22">
+    <row r="374" spans="1:22" ht="14.4">
       <c r="A374" s="15" t="s">
         <v>423</v>
       </c>
@@ -29315,8 +29323,8 @@
       <c r="K374" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L374" s="29" t="s">
-        <v>13</v>
+      <c r="L374" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M374" s="27">
         <v>24</v>
@@ -29347,7 +29355,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="375" spans="1:22">
+    <row r="375" spans="1:22" ht="14.4">
       <c r="A375" s="15" t="s">
         <v>423</v>
       </c>
@@ -29381,8 +29389,8 @@
       <c r="K375" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L375" s="29" t="s">
-        <v>13</v>
+      <c r="L375" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M375" s="27">
         <v>24</v>
@@ -29415,7 +29423,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="376" spans="1:22">
+    <row r="376" spans="1:22" ht="14.4">
       <c r="A376" s="15" t="s">
         <v>423</v>
       </c>
@@ -29449,8 +29457,8 @@
       <c r="K376" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L376" s="29" t="s">
-        <v>13</v>
+      <c r="L376" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M376" s="27">
         <v>24</v>
@@ -29481,7 +29489,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="377" spans="1:22">
+    <row r="377" spans="1:22" ht="14.4">
       <c r="A377" s="15" t="s">
         <v>423</v>
       </c>
@@ -29515,8 +29523,8 @@
       <c r="K377" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L377" s="29" t="s">
-        <v>13</v>
+      <c r="L377" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M377" s="27">
         <v>24</v>
@@ -29549,7 +29557,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="378" spans="1:22">
+    <row r="378" spans="1:22" ht="14.4">
       <c r="A378" s="15" t="s">
         <v>425</v>
       </c>
@@ -29583,8 +29591,8 @@
       <c r="K378" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L378" s="29" t="s">
-        <v>13</v>
+      <c r="L378" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M378" s="27">
         <v>6</v>
@@ -29615,7 +29623,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="379" spans="1:22">
+    <row r="379" spans="1:22" ht="14.4">
       <c r="A379" s="15" t="s">
         <v>425</v>
       </c>
@@ -29649,8 +29657,8 @@
       <c r="K379" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L379" s="29" t="s">
-        <v>13</v>
+      <c r="L379" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M379" s="27">
         <v>6</v>
@@ -29683,7 +29691,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="380" spans="1:22">
+    <row r="380" spans="1:22" ht="14.4">
       <c r="A380" s="15" t="s">
         <v>425</v>
       </c>
@@ -29717,8 +29725,8 @@
       <c r="K380" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L380" s="29" t="s">
-        <v>13</v>
+      <c r="L380" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M380" s="27">
         <v>6</v>
@@ -29749,7 +29757,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="381" spans="1:22">
+    <row r="381" spans="1:22" ht="14.4">
       <c r="A381" s="15" t="s">
         <v>425</v>
       </c>
@@ -29783,8 +29791,8 @@
       <c r="K381" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L381" s="29" t="s">
-        <v>13</v>
+      <c r="L381" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M381" s="27">
         <v>6</v>
@@ -29817,7 +29825,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="382" spans="1:22">
+    <row r="382" spans="1:22" ht="14.4">
       <c r="A382" s="15" t="s">
         <v>428</v>
       </c>
@@ -29851,8 +29859,8 @@
       <c r="K382" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L382" s="29" t="s">
-        <v>13</v>
+      <c r="L382" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M382" s="27">
         <v>18</v>
@@ -29883,7 +29891,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="383" spans="1:22">
+    <row r="383" spans="1:22" ht="14.4">
       <c r="A383" s="15" t="s">
         <v>428</v>
       </c>
@@ -29917,8 +29925,8 @@
       <c r="K383" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L383" s="29" t="s">
-        <v>13</v>
+      <c r="L383" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M383" s="27">
         <v>18</v>
@@ -29951,7 +29959,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="384" spans="1:22">
+    <row r="384" spans="1:22" ht="14.4">
       <c r="A384" s="15" t="s">
         <v>428</v>
       </c>
@@ -29985,8 +29993,8 @@
       <c r="K384" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L384" s="29" t="s">
-        <v>13</v>
+      <c r="L384" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M384" s="27">
         <v>18</v>
@@ -30017,7 +30025,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="385" spans="1:22">
+    <row r="385" spans="1:22" ht="14.4">
       <c r="A385" s="15" t="s">
         <v>428</v>
       </c>
@@ -30051,8 +30059,8 @@
       <c r="K385" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L385" s="29" t="s">
-        <v>13</v>
+      <c r="L385" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M385" s="27">
         <v>18</v>
@@ -30085,7 +30093,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="386" spans="1:22">
+    <row r="386" spans="1:22" ht="14.4">
       <c r="A386" s="15" t="s">
         <v>431</v>
       </c>
@@ -30119,8 +30127,8 @@
       <c r="K386" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L386" s="29" t="s">
-        <v>13</v>
+      <c r="L386" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M386" s="27">
         <v>12</v>
@@ -30151,7 +30159,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="387" spans="1:22">
+    <row r="387" spans="1:22" ht="14.4">
       <c r="A387" s="15" t="s">
         <v>431</v>
       </c>
@@ -30185,8 +30193,8 @@
       <c r="K387" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L387" s="29" t="s">
-        <v>13</v>
+      <c r="L387" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M387" s="27">
         <v>12</v>
@@ -30219,7 +30227,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="388" spans="1:22">
+    <row r="388" spans="1:22" ht="14.4">
       <c r="A388" s="15" t="s">
         <v>431</v>
       </c>
@@ -30253,8 +30261,8 @@
       <c r="K388" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L388" s="29" t="s">
-        <v>13</v>
+      <c r="L388" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M388" s="27">
         <v>12</v>
@@ -30285,7 +30293,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="389" spans="1:22">
+    <row r="389" spans="1:22" ht="14.4">
       <c r="A389" s="15" t="s">
         <v>431</v>
       </c>
@@ -30319,8 +30327,8 @@
       <c r="K389" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L389" s="29" t="s">
-        <v>13</v>
+      <c r="L389" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M389" s="27">
         <v>12</v>
@@ -30353,7 +30361,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="390" spans="1:22">
+    <row r="390" spans="1:22" ht="14.4">
       <c r="A390" s="15" t="s">
         <v>434</v>
       </c>
@@ -30387,8 +30395,8 @@
       <c r="K390" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L390" s="29" t="s">
-        <v>13</v>
+      <c r="L390" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M390" s="27">
         <v>12</v>
@@ -30419,7 +30427,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="391" spans="1:22">
+    <row r="391" spans="1:22" ht="14.4">
       <c r="A391" s="15" t="s">
         <v>434</v>
       </c>
@@ -30453,8 +30461,8 @@
       <c r="K391" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L391" s="29" t="s">
-        <v>13</v>
+      <c r="L391" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M391" s="27">
         <v>12</v>
@@ -30487,7 +30495,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="392" spans="1:22">
+    <row r="392" spans="1:22" ht="14.4">
       <c r="A392" s="15" t="s">
         <v>434</v>
       </c>
@@ -30521,8 +30529,8 @@
       <c r="K392" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L392" s="29" t="s">
-        <v>13</v>
+      <c r="L392" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M392" s="27">
         <v>12</v>
@@ -30553,7 +30561,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="393" spans="1:22">
+    <row r="393" spans="1:22" ht="14.4">
       <c r="A393" s="15" t="s">
         <v>434</v>
       </c>
@@ -30587,8 +30595,8 @@
       <c r="K393" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L393" s="29" t="s">
-        <v>13</v>
+      <c r="L393" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M393" s="27">
         <v>12</v>
@@ -30621,7 +30629,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="394" spans="1:22">
+    <row r="394" spans="1:22" ht="14.4">
       <c r="A394" s="15" t="s">
         <v>437</v>
       </c>
@@ -30655,8 +30663,8 @@
       <c r="K394" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L394" s="29" t="s">
-        <v>13</v>
+      <c r="L394" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M394" s="27">
         <v>24</v>
@@ -30687,7 +30695,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="395" spans="1:22">
+    <row r="395" spans="1:22" ht="14.4">
       <c r="A395" s="15" t="s">
         <v>437</v>
       </c>
@@ -30721,8 +30729,8 @@
       <c r="K395" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L395" s="29" t="s">
-        <v>13</v>
+      <c r="L395" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M395" s="27">
         <v>24</v>
@@ -30755,7 +30763,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="396" spans="1:22">
+    <row r="396" spans="1:22" ht="14.4">
       <c r="A396" s="15" t="s">
         <v>437</v>
       </c>
@@ -30789,8 +30797,8 @@
       <c r="K396" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L396" s="29" t="s">
-        <v>13</v>
+      <c r="L396" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M396" s="27">
         <v>24</v>
@@ -30821,7 +30829,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="397" spans="1:22">
+    <row r="397" spans="1:22" ht="14.4">
       <c r="A397" s="15" t="s">
         <v>437</v>
       </c>
@@ -30855,8 +30863,8 @@
       <c r="K397" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L397" s="29" t="s">
-        <v>13</v>
+      <c r="L397" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M397" s="27">
         <v>24</v>
@@ -30889,7 +30897,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="398" spans="1:22">
+    <row r="398" spans="1:22" ht="14.4">
       <c r="A398" s="15" t="s">
         <v>668</v>
       </c>
@@ -30923,8 +30931,8 @@
       <c r="K398" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L398" s="29" t="s">
-        <v>13</v>
+      <c r="L398" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M398" s="27">
         <v>6</v>
@@ -30955,7 +30963,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="399" spans="1:22">
+    <row r="399" spans="1:22" ht="14.4">
       <c r="A399" s="15" t="s">
         <v>668</v>
       </c>
@@ -30989,8 +30997,8 @@
       <c r="K399" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L399" s="29" t="s">
-        <v>13</v>
+      <c r="L399" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M399" s="27">
         <v>6</v>
@@ -31023,7 +31031,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="400" spans="1:22">
+    <row r="400" spans="1:22" ht="14.4">
       <c r="A400" s="15" t="s">
         <v>668</v>
       </c>
@@ -31057,8 +31065,8 @@
       <c r="K400" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L400" s="29" t="s">
-        <v>13</v>
+      <c r="L400" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M400" s="27">
         <v>6</v>
@@ -31089,7 +31097,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="401" spans="1:22">
+    <row r="401" spans="1:22" ht="14.4">
       <c r="A401" s="15" t="s">
         <v>668</v>
       </c>
@@ -31123,8 +31131,8 @@
       <c r="K401" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L401" s="29" t="s">
-        <v>13</v>
+      <c r="L401" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M401" s="27">
         <v>6</v>
@@ -31157,7 +31165,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="402" spans="1:22">
+    <row r="402" spans="1:22" ht="14.4">
       <c r="A402" s="15" t="s">
         <v>672</v>
       </c>
@@ -31191,8 +31199,8 @@
       <c r="K402" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L402" s="29" t="s">
-        <v>13</v>
+      <c r="L402" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M402" s="27">
         <v>18</v>
@@ -31223,7 +31231,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="403" spans="1:22">
+    <row r="403" spans="1:22" ht="14.4">
       <c r="A403" s="15" t="s">
         <v>672</v>
       </c>
@@ -31257,8 +31265,8 @@
       <c r="K403" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L403" s="29" t="s">
-        <v>13</v>
+      <c r="L403" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M403" s="27">
         <v>18</v>
@@ -31291,7 +31299,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="404" spans="1:22">
+    <row r="404" spans="1:22" ht="14.4">
       <c r="A404" s="15" t="s">
         <v>672</v>
       </c>
@@ -31325,8 +31333,8 @@
       <c r="K404" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L404" s="29" t="s">
-        <v>13</v>
+      <c r="L404" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M404" s="27">
         <v>18</v>
@@ -31357,7 +31365,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="405" spans="1:22">
+    <row r="405" spans="1:22" ht="14.4">
       <c r="A405" s="15" t="s">
         <v>672</v>
       </c>
@@ -31391,8 +31399,8 @@
       <c r="K405" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L405" s="29" t="s">
-        <v>13</v>
+      <c r="L405" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M405" s="27">
         <v>18</v>
@@ -31425,7 +31433,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="406" spans="1:22">
+    <row r="406" spans="1:22" ht="14.4">
       <c r="A406" s="15" t="s">
         <v>675</v>
       </c>
@@ -31459,8 +31467,8 @@
       <c r="K406" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L406" s="29" t="s">
-        <v>13</v>
+      <c r="L406" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M406" s="27">
         <v>12</v>
@@ -31491,7 +31499,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="407" spans="1:22">
+    <row r="407" spans="1:22" ht="14.4">
       <c r="A407" s="15" t="s">
         <v>675</v>
       </c>
@@ -31525,8 +31533,8 @@
       <c r="K407" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L407" s="29" t="s">
-        <v>13</v>
+      <c r="L407" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M407" s="27">
         <v>12</v>
@@ -31559,7 +31567,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="408" spans="1:22">
+    <row r="408" spans="1:22" ht="14.4">
       <c r="A408" s="15" t="s">
         <v>675</v>
       </c>
@@ -31593,8 +31601,8 @@
       <c r="K408" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L408" s="29" t="s">
-        <v>13</v>
+      <c r="L408" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M408" s="27">
         <v>12</v>
@@ -31625,7 +31633,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="409" spans="1:22">
+    <row r="409" spans="1:22" ht="14.4">
       <c r="A409" s="15" t="s">
         <v>675</v>
       </c>
@@ -31659,8 +31667,8 @@
       <c r="K409" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L409" s="29" t="s">
-        <v>13</v>
+      <c r="L409" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M409" s="27">
         <v>12</v>
@@ -31693,7 +31701,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="410" spans="1:22">
+    <row r="410" spans="1:22" ht="14.4">
       <c r="A410" s="15" t="s">
         <v>678</v>
       </c>
@@ -31727,8 +31735,8 @@
       <c r="K410" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L410" s="29" t="s">
-        <v>13</v>
+      <c r="L410" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M410" s="27">
         <v>12</v>
@@ -31759,7 +31767,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="411" spans="1:22">
+    <row r="411" spans="1:22" ht="14.4">
       <c r="A411" s="15" t="s">
         <v>678</v>
       </c>
@@ -31793,8 +31801,8 @@
       <c r="K411" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L411" s="29" t="s">
-        <v>13</v>
+      <c r="L411" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M411" s="27">
         <v>12</v>
@@ -31827,7 +31835,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="412" spans="1:22">
+    <row r="412" spans="1:22" ht="14.4">
       <c r="A412" s="15" t="s">
         <v>678</v>
       </c>
@@ -31861,8 +31869,8 @@
       <c r="K412" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L412" s="29" t="s">
-        <v>13</v>
+      <c r="L412" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M412" s="27">
         <v>12</v>
@@ -31893,7 +31901,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="413" spans="1:22">
+    <row r="413" spans="1:22" ht="14.4">
       <c r="A413" s="15" t="s">
         <v>678</v>
       </c>
@@ -31927,8 +31935,8 @@
       <c r="K413" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L413" s="29" t="s">
-        <v>13</v>
+      <c r="L413" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M413" s="27">
         <v>12</v>
@@ -31961,7 +31969,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="414" spans="1:22">
+    <row r="414" spans="1:22" ht="14.4">
       <c r="A414" s="15" t="s">
         <v>681</v>
       </c>
@@ -31995,8 +32003,8 @@
       <c r="K414" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L414" s="29" t="s">
-        <v>13</v>
+      <c r="L414" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M414" s="27">
         <v>24</v>
@@ -32027,7 +32035,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="415" spans="1:22">
+    <row r="415" spans="1:22" ht="14.4">
       <c r="A415" s="15" t="s">
         <v>681</v>
       </c>
@@ -32061,8 +32069,8 @@
       <c r="K415" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L415" s="29" t="s">
-        <v>13</v>
+      <c r="L415" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M415" s="27">
         <v>24</v>
@@ -32095,7 +32103,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="416" spans="1:22">
+    <row r="416" spans="1:22" ht="14.4">
       <c r="A416" s="15" t="s">
         <v>681</v>
       </c>
@@ -32129,8 +32137,8 @@
       <c r="K416" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L416" s="29" t="s">
-        <v>13</v>
+      <c r="L416" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M416" s="27">
         <v>24</v>
@@ -32161,7 +32169,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="417" spans="1:22">
+    <row r="417" spans="1:22" ht="14.4">
       <c r="A417" s="15" t="s">
         <v>681</v>
       </c>
@@ -32195,8 +32203,8 @@
       <c r="K417" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L417" s="29" t="s">
-        <v>13</v>
+      <c r="L417" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M417" s="27">
         <v>24</v>
@@ -32229,7 +32237,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="418" spans="1:22">
+    <row r="418" spans="1:22" ht="14.4">
       <c r="A418" s="15" t="s">
         <v>683</v>
       </c>
@@ -32263,8 +32271,8 @@
       <c r="K418" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L418" s="29" t="s">
-        <v>13</v>
+      <c r="L418" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M418" s="27">
         <v>6</v>
@@ -32295,7 +32303,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="419" spans="1:22">
+    <row r="419" spans="1:22" ht="14.4">
       <c r="A419" s="15" t="s">
         <v>683</v>
       </c>
@@ -32329,8 +32337,8 @@
       <c r="K419" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L419" s="29" t="s">
-        <v>13</v>
+      <c r="L419" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M419" s="27">
         <v>6</v>
@@ -32363,7 +32371,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="420" spans="1:22">
+    <row r="420" spans="1:22" ht="14.4">
       <c r="A420" s="15" t="s">
         <v>683</v>
       </c>
@@ -32397,8 +32405,8 @@
       <c r="K420" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L420" s="29" t="s">
-        <v>13</v>
+      <c r="L420" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M420" s="27">
         <v>6</v>
@@ -32429,7 +32437,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="421" spans="1:22">
+    <row r="421" spans="1:22" ht="14.4">
       <c r="A421" s="15" t="s">
         <v>683</v>
       </c>
@@ -32463,8 +32471,8 @@
       <c r="K421" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L421" s="29" t="s">
-        <v>13</v>
+      <c r="L421" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M421" s="27">
         <v>6</v>
@@ -32497,7 +32505,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="422" spans="1:22">
+    <row r="422" spans="1:22" ht="14.4">
       <c r="A422" s="15" t="s">
         <v>686</v>
       </c>
@@ -32531,8 +32539,8 @@
       <c r="K422" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L422" s="29" t="s">
-        <v>13</v>
+      <c r="L422" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M422" s="27">
         <v>18</v>
@@ -32563,7 +32571,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="423" spans="1:22">
+    <row r="423" spans="1:22" ht="14.4">
       <c r="A423" s="15" t="s">
         <v>686</v>
       </c>
@@ -32597,8 +32605,8 @@
       <c r="K423" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L423" s="29" t="s">
-        <v>13</v>
+      <c r="L423" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M423" s="27">
         <v>18</v>
@@ -32631,7 +32639,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="424" spans="1:22">
+    <row r="424" spans="1:22" ht="14.4">
       <c r="A424" s="15" t="s">
         <v>686</v>
       </c>
@@ -32665,8 +32673,8 @@
       <c r="K424" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L424" s="29" t="s">
-        <v>13</v>
+      <c r="L424" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M424" s="27">
         <v>18</v>
@@ -32697,7 +32705,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="425" spans="1:22">
+    <row r="425" spans="1:22" ht="14.4">
       <c r="A425" s="15" t="s">
         <v>686</v>
       </c>
@@ -32731,8 +32739,8 @@
       <c r="K425" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L425" s="29" t="s">
-        <v>13</v>
+      <c r="L425" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M425" s="27">
         <v>18</v>
@@ -32765,7 +32773,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="426" spans="1:22">
+    <row r="426" spans="1:22" ht="14.4">
       <c r="A426" s="15" t="s">
         <v>688</v>
       </c>
@@ -32799,8 +32807,8 @@
       <c r="K426" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L426" s="29" t="s">
-        <v>13</v>
+      <c r="L426" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M426" s="27">
         <v>12</v>
@@ -32831,7 +32839,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="427" spans="1:22">
+    <row r="427" spans="1:22" ht="14.4">
       <c r="A427" s="15" t="s">
         <v>688</v>
       </c>
@@ -32865,8 +32873,8 @@
       <c r="K427" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L427" s="29" t="s">
-        <v>13</v>
+      <c r="L427" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M427" s="27">
         <v>12</v>
@@ -32899,7 +32907,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="428" spans="1:22">
+    <row r="428" spans="1:22" ht="14.4">
       <c r="A428" s="15" t="s">
         <v>688</v>
       </c>
@@ -32933,8 +32941,8 @@
       <c r="K428" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L428" s="29" t="s">
-        <v>13</v>
+      <c r="L428" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M428" s="27">
         <v>12</v>
@@ -32965,7 +32973,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="429" spans="1:22">
+    <row r="429" spans="1:22" ht="14.4">
       <c r="A429" s="15" t="s">
         <v>688</v>
       </c>
@@ -32999,8 +33007,8 @@
       <c r="K429" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L429" s="29" t="s">
-        <v>13</v>
+      <c r="L429" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M429" s="27">
         <v>12</v>
@@ -33033,7 +33041,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="430" spans="1:22">
+    <row r="430" spans="1:22" ht="14.4">
       <c r="A430" s="15" t="s">
         <v>690</v>
       </c>
@@ -33067,8 +33075,8 @@
       <c r="K430" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L430" s="29" t="s">
-        <v>13</v>
+      <c r="L430" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M430" s="27">
         <v>12</v>
@@ -33099,7 +33107,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="431" spans="1:22">
+    <row r="431" spans="1:22" ht="14.4">
       <c r="A431" s="15" t="s">
         <v>690</v>
       </c>
@@ -33133,8 +33141,8 @@
       <c r="K431" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L431" s="29" t="s">
-        <v>13</v>
+      <c r="L431" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M431" s="27">
         <v>12</v>
@@ -33167,7 +33175,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="432" spans="1:22">
+    <row r="432" spans="1:22" ht="14.4">
       <c r="A432" s="15" t="s">
         <v>690</v>
       </c>
@@ -33201,8 +33209,8 @@
       <c r="K432" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L432" s="29" t="s">
-        <v>13</v>
+      <c r="L432" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M432" s="27">
         <v>12</v>
@@ -33233,7 +33241,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="433" spans="1:22">
+    <row r="433" spans="1:22" ht="14.4">
       <c r="A433" s="15" t="s">
         <v>690</v>
       </c>
@@ -33267,8 +33275,8 @@
       <c r="K433" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L433" s="29" t="s">
-        <v>13</v>
+      <c r="L433" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M433" s="27">
         <v>12</v>
@@ -33301,7 +33309,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="434" spans="1:22">
+    <row r="434" spans="1:22" ht="14.4">
       <c r="A434" s="15" t="s">
         <v>693</v>
       </c>
@@ -33335,8 +33343,8 @@
       <c r="K434" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L434" s="29" t="s">
-        <v>13</v>
+      <c r="L434" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M434" s="27">
         <v>24</v>
@@ -33367,7 +33375,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="435" spans="1:22">
+    <row r="435" spans="1:22" ht="14.4">
       <c r="A435" s="15" t="s">
         <v>693</v>
       </c>
@@ -33401,8 +33409,8 @@
       <c r="K435" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L435" s="29" t="s">
-        <v>13</v>
+      <c r="L435" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M435" s="27">
         <v>24</v>
@@ -33435,7 +33443,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="436" spans="1:22">
+    <row r="436" spans="1:22" ht="14.4">
       <c r="A436" s="15" t="s">
         <v>693</v>
       </c>
@@ -33469,8 +33477,8 @@
       <c r="K436" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L436" s="29" t="s">
-        <v>13</v>
+      <c r="L436" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M436" s="27">
         <v>24</v>
@@ -33501,7 +33509,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="437" spans="1:22">
+    <row r="437" spans="1:22" ht="14.4">
       <c r="A437" s="15" t="s">
         <v>693</v>
       </c>
@@ -33535,8 +33543,8 @@
       <c r="K437" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L437" s="29" t="s">
-        <v>13</v>
+      <c r="L437" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M437" s="27">
         <v>24</v>
@@ -33569,7 +33577,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="438" spans="1:22">
+    <row r="438" spans="1:22" ht="14.4">
       <c r="A438" s="15" t="s">
         <v>697</v>
       </c>
@@ -33603,8 +33611,8 @@
       <c r="K438" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L438" s="29" t="s">
-        <v>13</v>
+      <c r="L438" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M438" s="27">
         <v>6</v>
@@ -33635,7 +33643,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="439" spans="1:22">
+    <row r="439" spans="1:22" ht="14.4">
       <c r="A439" s="15" t="s">
         <v>697</v>
       </c>
@@ -33669,8 +33677,8 @@
       <c r="K439" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L439" s="29" t="s">
-        <v>13</v>
+      <c r="L439" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M439" s="27">
         <v>6</v>
@@ -33703,7 +33711,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="440" spans="1:22">
+    <row r="440" spans="1:22" ht="14.4">
       <c r="A440" s="15" t="s">
         <v>697</v>
       </c>
@@ -33737,8 +33745,8 @@
       <c r="K440" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L440" s="29" t="s">
-        <v>13</v>
+      <c r="L440" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M440" s="27">
         <v>6</v>
@@ -33769,7 +33777,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="441" spans="1:22">
+    <row r="441" spans="1:22" ht="14.4">
       <c r="A441" s="15" t="s">
         <v>697</v>
       </c>
@@ -33803,8 +33811,8 @@
       <c r="K441" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L441" s="29" t="s">
-        <v>13</v>
+      <c r="L441" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M441" s="27">
         <v>6</v>
@@ -33837,7 +33845,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="442" spans="1:22">
+    <row r="442" spans="1:22" ht="14.4">
       <c r="A442" s="15" t="s">
         <v>701</v>
       </c>
@@ -33871,8 +33879,8 @@
       <c r="K442" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L442" s="29" t="s">
-        <v>13</v>
+      <c r="L442" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M442" s="27">
         <v>18</v>
@@ -33903,7 +33911,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="443" spans="1:22">
+    <row r="443" spans="1:22" ht="14.4">
       <c r="A443" s="15" t="s">
         <v>701</v>
       </c>
@@ -33937,8 +33945,8 @@
       <c r="K443" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L443" s="29" t="s">
-        <v>13</v>
+      <c r="L443" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M443" s="27">
         <v>18</v>
@@ -33971,7 +33979,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="444" spans="1:22">
+    <row r="444" spans="1:22" ht="14.4">
       <c r="A444" s="15" t="s">
         <v>701</v>
       </c>
@@ -34005,8 +34013,8 @@
       <c r="K444" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L444" s="29" t="s">
-        <v>13</v>
+      <c r="L444" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M444" s="27">
         <v>18</v>
@@ -34037,7 +34045,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="445" spans="1:22">
+    <row r="445" spans="1:22" ht="14.4">
       <c r="A445" s="15" t="s">
         <v>701</v>
       </c>
@@ -34071,8 +34079,8 @@
       <c r="K445" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L445" s="29" t="s">
-        <v>13</v>
+      <c r="L445" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M445" s="27">
         <v>18</v>
@@ -34105,7 +34113,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="446" spans="1:22">
+    <row r="446" spans="1:22" ht="14.4">
       <c r="A446" s="15" t="s">
         <v>704</v>
       </c>
@@ -34139,8 +34147,8 @@
       <c r="K446" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L446" s="29" t="s">
-        <v>13</v>
+      <c r="L446" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M446" s="27">
         <v>12</v>
@@ -34171,7 +34179,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="447" spans="1:22">
+    <row r="447" spans="1:22" ht="14.4">
       <c r="A447" s="15" t="s">
         <v>704</v>
       </c>
@@ -34205,8 +34213,8 @@
       <c r="K447" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L447" s="29" t="s">
-        <v>13</v>
+      <c r="L447" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M447" s="27">
         <v>12</v>
@@ -34239,7 +34247,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="448" spans="1:22">
+    <row r="448" spans="1:22" ht="14.4">
       <c r="A448" s="15" t="s">
         <v>704</v>
       </c>
@@ -34273,8 +34281,8 @@
       <c r="K448" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L448" s="29" t="s">
-        <v>13</v>
+      <c r="L448" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M448" s="27">
         <v>12</v>
@@ -34305,7 +34313,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="449" spans="1:22">
+    <row r="449" spans="1:22" ht="14.4">
       <c r="A449" s="15" t="s">
         <v>704</v>
       </c>
@@ -34339,8 +34347,8 @@
       <c r="K449" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L449" s="29" t="s">
-        <v>13</v>
+      <c r="L449" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M449" s="27">
         <v>12</v>
@@ -34373,7 +34381,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="450" spans="1:22">
+    <row r="450" spans="1:22" ht="14.4">
       <c r="A450" s="15" t="s">
         <v>707</v>
       </c>
@@ -34407,8 +34415,8 @@
       <c r="K450" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L450" s="29" t="s">
-        <v>13</v>
+      <c r="L450" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M450" s="27">
         <v>12</v>
@@ -34439,7 +34447,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="451" spans="1:22">
+    <row r="451" spans="1:22" ht="14.4">
       <c r="A451" s="15" t="s">
         <v>707</v>
       </c>
@@ -34473,8 +34481,8 @@
       <c r="K451" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L451" s="29" t="s">
-        <v>13</v>
+      <c r="L451" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M451" s="27">
         <v>12</v>
@@ -34507,7 +34515,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="452" spans="1:22">
+    <row r="452" spans="1:22" ht="14.4">
       <c r="A452" s="15" t="s">
         <v>707</v>
       </c>
@@ -34541,8 +34549,8 @@
       <c r="K452" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L452" s="29" t="s">
-        <v>13</v>
+      <c r="L452" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M452" s="27">
         <v>12</v>
@@ -34573,7 +34581,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="453" spans="1:22">
+    <row r="453" spans="1:22" ht="14.4">
       <c r="A453" s="15" t="s">
         <v>707</v>
       </c>
@@ -34607,8 +34615,8 @@
       <c r="K453" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L453" s="29" t="s">
-        <v>13</v>
+      <c r="L453" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M453" s="27">
         <v>12</v>
@@ -34641,7 +34649,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="454" spans="1:22">
+    <row r="454" spans="1:22" ht="14.4">
       <c r="A454" s="15" t="s">
         <v>709</v>
       </c>
@@ -34675,8 +34683,8 @@
       <c r="K454" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L454" s="29" t="s">
-        <v>13</v>
+      <c r="L454" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M454" s="27">
         <v>24</v>
@@ -34707,7 +34715,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="455" spans="1:22">
+    <row r="455" spans="1:22" ht="14.4">
       <c r="A455" s="15" t="s">
         <v>709</v>
       </c>
@@ -34741,8 +34749,8 @@
       <c r="K455" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L455" s="29" t="s">
-        <v>13</v>
+      <c r="L455" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M455" s="27">
         <v>24</v>
@@ -34775,7 +34783,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="456" spans="1:22">
+    <row r="456" spans="1:22" ht="14.4">
       <c r="A456" s="15" t="s">
         <v>709</v>
       </c>
@@ -34809,8 +34817,8 @@
       <c r="K456" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L456" s="29" t="s">
-        <v>13</v>
+      <c r="L456" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M456" s="27">
         <v>24</v>
@@ -34841,7 +34849,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="457" spans="1:22">
+    <row r="457" spans="1:22" ht="14.4">
       <c r="A457" s="15" t="s">
         <v>709</v>
       </c>
@@ -34875,8 +34883,8 @@
       <c r="K457" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L457" s="29" t="s">
-        <v>13</v>
+      <c r="L457" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M457" s="27">
         <v>24</v>
@@ -34909,7 +34917,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="458" spans="1:22">
+    <row r="458" spans="1:22" ht="14.4">
       <c r="A458" s="15" t="s">
         <v>711</v>
       </c>
@@ -34943,8 +34951,8 @@
       <c r="K458" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L458" s="29" t="s">
-        <v>13</v>
+      <c r="L458" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M458" s="27">
         <v>6</v>
@@ -34975,7 +34983,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="459" spans="1:22">
+    <row r="459" spans="1:22" ht="14.4">
       <c r="A459" s="15" t="s">
         <v>711</v>
       </c>
@@ -35009,8 +35017,8 @@
       <c r="K459" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L459" s="29" t="s">
-        <v>13</v>
+      <c r="L459" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M459" s="27">
         <v>6</v>
@@ -35043,7 +35051,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="460" spans="1:22">
+    <row r="460" spans="1:22" ht="14.4">
       <c r="A460" s="15" t="s">
         <v>711</v>
       </c>
@@ -35077,8 +35085,8 @@
       <c r="K460" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L460" s="29" t="s">
-        <v>13</v>
+      <c r="L460" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M460" s="27">
         <v>6</v>
@@ -35109,7 +35117,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="461" spans="1:22">
+    <row r="461" spans="1:22" ht="14.4">
       <c r="A461" s="15" t="s">
         <v>711</v>
       </c>
@@ -35143,8 +35151,8 @@
       <c r="K461" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L461" s="29" t="s">
-        <v>13</v>
+      <c r="L461" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M461" s="27">
         <v>6</v>
@@ -35177,7 +35185,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="462" spans="1:22">
+    <row r="462" spans="1:22" ht="14.4">
       <c r="A462" s="15" t="s">
         <v>714</v>
       </c>
@@ -35211,8 +35219,8 @@
       <c r="K462" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L462" s="29" t="s">
-        <v>13</v>
+      <c r="L462" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M462" s="27">
         <v>18</v>
@@ -35243,7 +35251,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="463" spans="1:22">
+    <row r="463" spans="1:22" ht="14.4">
       <c r="A463" s="15" t="s">
         <v>714</v>
       </c>
@@ -35277,8 +35285,8 @@
       <c r="K463" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L463" s="29" t="s">
-        <v>13</v>
+      <c r="L463" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M463" s="27">
         <v>18</v>
@@ -35311,7 +35319,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="464" spans="1:22">
+    <row r="464" spans="1:22" ht="14.4">
       <c r="A464" s="15" t="s">
         <v>714</v>
       </c>
@@ -35345,8 +35353,8 @@
       <c r="K464" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L464" s="29" t="s">
-        <v>13</v>
+      <c r="L464" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M464" s="27">
         <v>18</v>
@@ -35377,7 +35385,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="465" spans="1:22">
+    <row r="465" spans="1:22" ht="14.4">
       <c r="A465" s="15" t="s">
         <v>714</v>
       </c>
@@ -35411,8 +35419,8 @@
       <c r="K465" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L465" s="29" t="s">
-        <v>13</v>
+      <c r="L465" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M465" s="27">
         <v>18</v>
@@ -35445,7 +35453,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="466" spans="1:22">
+    <row r="466" spans="1:22" ht="14.4">
       <c r="A466" s="15" t="s">
         <v>717</v>
       </c>
@@ -35479,8 +35487,8 @@
       <c r="K466" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L466" s="29" t="s">
-        <v>13</v>
+      <c r="L466" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M466" s="27">
         <v>12</v>
@@ -35511,7 +35519,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="467" spans="1:22">
+    <row r="467" spans="1:22" ht="14.4">
       <c r="A467" s="15" t="s">
         <v>717</v>
       </c>
@@ -35545,8 +35553,8 @@
       <c r="K467" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L467" s="29" t="s">
-        <v>13</v>
+      <c r="L467" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M467" s="27">
         <v>12</v>
@@ -35579,7 +35587,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="468" spans="1:22">
+    <row r="468" spans="1:22" ht="14.4">
       <c r="A468" s="15" t="s">
         <v>717</v>
       </c>
@@ -35613,8 +35621,8 @@
       <c r="K468" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L468" s="29" t="s">
-        <v>13</v>
+      <c r="L468" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M468" s="27">
         <v>12</v>
@@ -35645,7 +35653,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="469" spans="1:22">
+    <row r="469" spans="1:22" ht="14.4">
       <c r="A469" s="15" t="s">
         <v>717</v>
       </c>
@@ -35679,8 +35687,8 @@
       <c r="K469" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L469" s="29" t="s">
-        <v>13</v>
+      <c r="L469" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M469" s="27">
         <v>12</v>
@@ -35713,7 +35721,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="470" spans="1:22">
+    <row r="470" spans="1:22" ht="14.4">
       <c r="A470" s="15" t="s">
         <v>720</v>
       </c>
@@ -35747,8 +35755,8 @@
       <c r="K470" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L470" s="29" t="s">
-        <v>13</v>
+      <c r="L470" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M470" s="27">
         <v>24</v>
@@ -35779,7 +35787,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="471" spans="1:22">
+    <row r="471" spans="1:22" ht="14.4">
       <c r="A471" s="15" t="s">
         <v>720</v>
       </c>
@@ -35813,8 +35821,8 @@
       <c r="K471" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L471" s="29" t="s">
-        <v>13</v>
+      <c r="L471" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M471" s="27">
         <v>24</v>
@@ -35847,7 +35855,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="472" spans="1:22">
+    <row r="472" spans="1:22" ht="14.4">
       <c r="A472" s="15" t="s">
         <v>720</v>
       </c>
@@ -35881,8 +35889,8 @@
       <c r="K472" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L472" s="29" t="s">
-        <v>13</v>
+      <c r="L472" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M472" s="27">
         <v>24</v>
@@ -35913,7 +35921,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="473" spans="1:22">
+    <row r="473" spans="1:22" ht="14.4">
       <c r="A473" s="15" t="s">
         <v>720</v>
       </c>
@@ -35947,8 +35955,8 @@
       <c r="K473" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L473" s="29" t="s">
-        <v>13</v>
+      <c r="L473" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M473" s="27">
         <v>24</v>
@@ -35981,7 +35989,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="474" spans="1:22">
+    <row r="474" spans="1:22" ht="14.4">
       <c r="A474" s="15" t="s">
         <v>723</v>
       </c>
@@ -36015,8 +36023,8 @@
       <c r="K474" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L474" s="29" t="s">
-        <v>13</v>
+      <c r="L474" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M474" s="27">
         <v>6</v>
@@ -36047,7 +36055,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="475" spans="1:22">
+    <row r="475" spans="1:22" ht="14.4">
       <c r="A475" s="15" t="s">
         <v>723</v>
       </c>
@@ -36081,8 +36089,8 @@
       <c r="K475" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L475" s="29" t="s">
-        <v>13</v>
+      <c r="L475" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M475" s="27">
         <v>6</v>
@@ -36115,7 +36123,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="476" spans="1:22">
+    <row r="476" spans="1:22" ht="14.4">
       <c r="A476" s="15" t="s">
         <v>723</v>
       </c>
@@ -36149,8 +36157,8 @@
       <c r="K476" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L476" s="29" t="s">
-        <v>13</v>
+      <c r="L476" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M476" s="27">
         <v>6</v>
@@ -36181,7 +36189,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="477" spans="1:22">
+    <row r="477" spans="1:22" ht="14.4">
       <c r="A477" s="15" t="s">
         <v>723</v>
       </c>
@@ -36215,8 +36223,8 @@
       <c r="K477" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L477" s="29" t="s">
-        <v>13</v>
+      <c r="L477" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M477" s="27">
         <v>6</v>
@@ -36249,7 +36257,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="478" spans="1:22">
+    <row r="478" spans="1:22" ht="14.4">
       <c r="A478" s="15" t="s">
         <v>725</v>
       </c>
@@ -36283,8 +36291,8 @@
       <c r="K478" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L478" s="29" t="s">
-        <v>13</v>
+      <c r="L478" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M478" s="27">
         <v>18</v>
@@ -36315,7 +36323,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="479" spans="1:22">
+    <row r="479" spans="1:22" ht="14.4">
       <c r="A479" s="15" t="s">
         <v>725</v>
       </c>
@@ -36349,8 +36357,8 @@
       <c r="K479" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L479" s="29" t="s">
-        <v>13</v>
+      <c r="L479" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M479" s="27">
         <v>18</v>
@@ -36383,7 +36391,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="480" spans="1:22">
+    <row r="480" spans="1:22" ht="14.4">
       <c r="A480" s="15" t="s">
         <v>725</v>
       </c>
@@ -36417,8 +36425,8 @@
       <c r="K480" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L480" s="29" t="s">
-        <v>13</v>
+      <c r="L480" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M480" s="27">
         <v>18</v>
@@ -36449,7 +36457,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="481" spans="1:22">
+    <row r="481" spans="1:22" ht="14.4">
       <c r="A481" s="15" t="s">
         <v>725</v>
       </c>
@@ -36483,8 +36491,8 @@
       <c r="K481" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="L481" s="29" t="s">
-        <v>13</v>
+      <c r="L481" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M481" s="27">
         <v>18</v>
@@ -36517,7 +36525,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="482" spans="1:22">
+    <row r="482" spans="1:22" ht="14.4">
       <c r="A482" s="15" t="s">
         <v>727</v>
       </c>
@@ -36551,8 +36559,8 @@
       <c r="K482" s="29" t="s">
         <v>955</v>
       </c>
-      <c r="L482" s="29" t="s">
-        <v>13</v>
+      <c r="L482" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M482" s="28" t="s">
         <v>443</v>
@@ -36585,7 +36593,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="483" spans="1:22">
+    <row r="483" spans="1:22" ht="14.4">
       <c r="A483" s="15" t="s">
         <v>733</v>
       </c>
@@ -36619,8 +36627,8 @@
       <c r="K483" s="29" t="s">
         <v>957</v>
       </c>
-      <c r="L483" s="29" t="s">
-        <v>13</v>
+      <c r="L483" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M483" s="28" t="s">
         <v>443</v>
@@ -36653,7 +36661,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="484" spans="1:22">
+    <row r="484" spans="1:22" ht="14.4">
       <c r="A484" s="15" t="s">
         <v>737</v>
       </c>
@@ -36687,8 +36695,8 @@
       <c r="K484" s="29" t="s">
         <v>959</v>
       </c>
-      <c r="L484" s="29" t="s">
-        <v>13</v>
+      <c r="L484" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M484" s="28" t="s">
         <v>443</v>
@@ -36721,7 +36729,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="485" spans="1:22">
+    <row r="485" spans="1:22" ht="14.4">
       <c r="A485" s="15" t="s">
         <v>740</v>
       </c>
@@ -36755,8 +36763,8 @@
       <c r="K485" s="29" t="s">
         <v>961</v>
       </c>
-      <c r="L485" s="29" t="s">
-        <v>13</v>
+      <c r="L485" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M485" s="28" t="s">
         <v>443</v>
@@ -36789,7 +36797,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="486" spans="1:22">
+    <row r="486" spans="1:22" ht="14.4">
       <c r="A486" s="15" t="s">
         <v>744</v>
       </c>
@@ -36823,8 +36831,8 @@
       <c r="K486" s="29" t="s">
         <v>963</v>
       </c>
-      <c r="L486" s="29" t="s">
-        <v>13</v>
+      <c r="L486" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M486" s="28" t="s">
         <v>443</v>
@@ -36857,7 +36865,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="487" spans="1:22">
+    <row r="487" spans="1:22" ht="14.4">
       <c r="A487" s="15" t="s">
         <v>748</v>
       </c>
@@ -36891,8 +36899,8 @@
       <c r="K487" s="29" t="s">
         <v>965</v>
       </c>
-      <c r="L487" s="29" t="s">
-        <v>13</v>
+      <c r="L487" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M487" s="28" t="s">
         <v>443</v>
@@ -36925,7 +36933,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="488" spans="1:22">
+    <row r="488" spans="1:22" ht="14.4">
       <c r="A488" s="15" t="s">
         <v>753</v>
       </c>
@@ -36959,8 +36967,8 @@
       <c r="K488" s="29" t="s">
         <v>967</v>
       </c>
-      <c r="L488" s="29" t="s">
-        <v>13</v>
+      <c r="L488" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M488" s="28" t="s">
         <v>443</v>
@@ -36993,7 +37001,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="489" spans="1:22">
+    <row r="489" spans="1:22" ht="14.4">
       <c r="A489" s="15" t="s">
         <v>756</v>
       </c>
@@ -37027,8 +37035,8 @@
       <c r="K489" s="29" t="s">
         <v>969</v>
       </c>
-      <c r="L489" s="29" t="s">
-        <v>13</v>
+      <c r="L489" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M489" s="28" t="s">
         <v>443</v>
@@ -37061,7 +37069,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="490" spans="1:22">
+    <row r="490" spans="1:22" ht="14.4">
       <c r="A490" s="15" t="s">
         <v>760</v>
       </c>
@@ -37095,8 +37103,8 @@
       <c r="K490" s="29" t="s">
         <v>971</v>
       </c>
-      <c r="L490" s="29" t="s">
-        <v>13</v>
+      <c r="L490" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M490" s="28" t="s">
         <v>443</v>
@@ -37129,7 +37137,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="491" spans="1:22">
+    <row r="491" spans="1:22" ht="14.4">
       <c r="A491" s="15" t="s">
         <v>764</v>
       </c>
@@ -37163,8 +37171,8 @@
       <c r="K491" s="29" t="s">
         <v>973</v>
       </c>
-      <c r="L491" s="29" t="s">
-        <v>13</v>
+      <c r="L491" s="32" t="s">
+        <v>975</v>
       </c>
       <c r="M491" s="28" t="s">
         <v>443</v>
@@ -37209,7 +37217,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB49652-7DC2-4CB9-8BC9-BBF4428EE3D9}">
   <dimension ref="A1:O85"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -37218,10 +37226,10 @@
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="18" style="8" customWidth="1"/>
     <col min="7" max="7" width="14" style="8" customWidth="1"/>
-    <col min="8" max="8" width="3.875" customWidth="1"/>
+    <col min="8" max="8" width="3.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -37298,7 +37306,7 @@
         <v>火</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75">
+    <row r="4" spans="1:15" ht="15">
       <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
@@ -37331,7 +37339,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75">
+    <row r="5" spans="1:15" ht="15">
       <c r="A5" s="2" t="s">
         <v>42</v>
       </c>
@@ -37364,7 +37372,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75">
+    <row r="6" spans="1:15" ht="15">
       <c r="A6" s="2" t="s">
         <v>43</v>
       </c>
@@ -37397,7 +37405,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.75">
+    <row r="7" spans="1:15" ht="15">
       <c r="A7" s="2" t="s">
         <v>45</v>
       </c>
@@ -37430,7 +37438,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75">
+    <row r="8" spans="1:15" ht="15">
       <c r="A8" s="2" t="s">
         <v>47</v>
       </c>
@@ -37463,7 +37471,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75">
+    <row r="9" spans="1:15" ht="15">
       <c r="A9" s="2" t="s">
         <v>48</v>
       </c>
@@ -37496,7 +37504,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75">
+    <row r="10" spans="1:15" ht="15">
       <c r="A10" s="2" t="s">
         <v>49</v>
       </c>
@@ -37610,7 +37618,7 @@
         <v>火</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15">
+    <row r="14" spans="1:15" ht="14.4">
       <c r="A14" s="2" t="s">
         <v>252</v>
       </c>
@@ -37772,7 +37780,7 @@
         <v>冰</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15">
+    <row r="20" spans="1:9" ht="14.4">
       <c r="A20" s="2" t="s">
         <v>230</v>
       </c>
